--- a/ComponentesMetodologicos/Normalizacion.xlsx
+++ b/ComponentesMetodologicos/Normalizacion.xlsx
@@ -1,34 +1,32 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SENA\Desktop\CEREBRUM\PROYECTO_CEREBRUM\ComponentesMetodologicos\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GABRIEL\PROYECTO_CEREBRUM\ComponentesMetodologicos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08BF7856-68B7-4204-AEE0-307AE0C548DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0AE4DB61-32B0-4EE7-97C4-A7C72E626100}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
+    <sheet name="1FN" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="156">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="388" uniqueCount="189">
   <si>
     <t>Cuenta</t>
   </si>
@@ -63,9 +61,6 @@
     <t>CU001</t>
   </si>
   <si>
-    <t>Ian Santiago Fernández Amaya</t>
-  </si>
-  <si>
     <t>Colegio San José</t>
   </si>
   <si>
@@ -81,39 +76,24 @@
     <t>CU003</t>
   </si>
   <si>
-    <t>Joseph Andrés Rivas Sánchez</t>
-  </si>
-  <si>
     <t>CU004</t>
   </si>
   <si>
-    <t>Pedro Eustaquio Pérez Silva</t>
-  </si>
-  <si>
     <t>Instituto Técnico Central</t>
   </si>
   <si>
     <t>CU005</t>
   </si>
   <si>
-    <t>María Fernanda León Quintana</t>
-  </si>
-  <si>
     <t>Colegio Santa María</t>
   </si>
   <si>
     <t>CU006</t>
   </si>
   <si>
-    <t>Sebastián Camilo Blandón Espitia</t>
-  </si>
-  <si>
     <t>CU007</t>
   </si>
   <si>
-    <t>Jorge Andrés Fernández Amaya</t>
-  </si>
-  <si>
     <t>Colegio Nueva Granada</t>
   </si>
   <si>
@@ -144,9 +124,6 @@
     <t>CU011</t>
   </si>
   <si>
-    <t>Anderson Exnehider Cunacue</t>
-  </si>
-  <si>
     <t>Colegio San Martín</t>
   </si>
   <si>
@@ -156,21 +133,12 @@
     <t>Iván Martínez</t>
   </si>
   <si>
-    <t>Colegio Los Andes</t>
-  </si>
-  <si>
     <t>CU013</t>
   </si>
   <si>
-    <t>Juan Esteban Hoyos Torres</t>
-  </si>
-  <si>
     <t>CU014</t>
   </si>
   <si>
-    <t>Karen Dayana Rivera Castro</t>
-  </si>
-  <si>
     <t>Colegio Nuestra Señora</t>
   </si>
   <si>
@@ -186,24 +154,12 @@
     <t>CU016</t>
   </si>
   <si>
-    <t>Ana Verónica Amaya Contreras</t>
-  </si>
-  <si>
     <t>CU017</t>
   </si>
   <si>
-    <t>John Alexander Peña</t>
-  </si>
-  <si>
-    <t>Colegio San Rafael</t>
-  </si>
-  <si>
     <t>CU018</t>
   </si>
   <si>
-    <t>Luis Alejandro Matoma Bocanegra</t>
-  </si>
-  <si>
     <t>Institución Educativa El Carmen</t>
   </si>
   <si>
@@ -496,13 +452,154 @@
   </si>
   <si>
     <t>Grupos y períodos, Ecuaciones, Ecosistemas</t>
+  </si>
+  <si>
+    <t>Jorge Fernández</t>
+  </si>
+  <si>
+    <t xml:space="preserve">María  León </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pedro  Pérez </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Joseph  Rivas </t>
+  </si>
+  <si>
+    <t>Santiago Fernández</t>
+  </si>
+  <si>
+    <t>Anderson  Cunacue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Karen Rivera </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ana  Amaya </t>
+  </si>
+  <si>
+    <t>John Peña</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Luis Matoma </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sebastián Blandón </t>
+  </si>
+  <si>
+    <t>Juan Hoyos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pedro Pérez </t>
+  </si>
+  <si>
+    <t xml:space="preserve">María León </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Matemáticas, </t>
+  </si>
+  <si>
+    <t>Física</t>
+  </si>
+  <si>
+    <t>Inglés</t>
+  </si>
+  <si>
+    <t>Gramática</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Movimiento</t>
+  </si>
+  <si>
+    <t>Álgebra</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Verbos</t>
+  </si>
+  <si>
+    <t>Velocidad</t>
+  </si>
+  <si>
+    <t>Lenguaje</t>
+  </si>
+  <si>
+    <t>Historia</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Colombia</t>
+  </si>
+  <si>
+    <t>Literatura</t>
+  </si>
+  <si>
+    <t>Géneros literarios</t>
+  </si>
+  <si>
+    <t>Constitución de 1991</t>
+  </si>
+  <si>
+    <t>Química</t>
+  </si>
+  <si>
+    <t>Matemáticas</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Energía</t>
+  </si>
+  <si>
+    <t>Geometría</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Energía cinética</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Ángulos</t>
+  </si>
+  <si>
+    <t>Propiedades físicas</t>
+  </si>
+  <si>
+    <t>Ciencias Naturales</t>
+  </si>
+  <si>
+    <t>Biología</t>
+  </si>
+  <si>
+    <t>Estadística</t>
+  </si>
+  <si>
+    <t>Media aritmética</t>
+  </si>
+  <si>
+    <t>La célula</t>
+  </si>
+  <si>
+    <t>CC-1001001007</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Lenguaje</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Comprensión lectora</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Edad Moderna</t>
+  </si>
+  <si>
+    <t>Renacimiento</t>
+  </si>
+  <si>
+    <t>Verbos irregulares</t>
+  </si>
+  <si>
+    <t>Idea principal</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -526,13 +623,43 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -563,7 +690,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -586,8 +713,36 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -921,7 +1076,7 @@
         <v>10</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>11</v>
+        <v>146</v>
       </c>
       <c r="C2" s="7">
         <v>46272</v>
@@ -930,30 +1085,30 @@
         <v>3104567821</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>81</v>
+        <v>67</v>
       </c>
       <c r="F2" s="8" t="s">
-        <v>61</v>
+        <v>47</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>100</v>
+        <v>86</v>
       </c>
       <c r="I2" s="6" t="s">
-        <v>118</v>
+        <v>104</v>
       </c>
       <c r="J2" s="6" t="s">
-        <v>119</v>
+        <v>105</v>
       </c>
     </row>
     <row r="3" spans="1:10" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3" s="6" t="s">
         <v>13</v>
-      </c>
-      <c r="B3" s="6" t="s">
-        <v>14</v>
       </c>
       <c r="C3" s="7">
         <v>46272</v>
@@ -962,30 +1117,30 @@
         <v>3115678932</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>94</v>
+        <v>80</v>
       </c>
       <c r="F3" s="9" t="s">
-        <v>62</v>
+        <v>48</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>101</v>
+        <v>87</v>
       </c>
       <c r="I3" s="6" t="s">
-        <v>120</v>
+        <v>106</v>
       </c>
       <c r="J3" s="6" t="s">
-        <v>121</v>
+        <v>107</v>
       </c>
     </row>
     <row r="4" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>17</v>
+        <v>145</v>
       </c>
       <c r="C4" s="7">
         <v>46272</v>
@@ -994,30 +1149,30 @@
         <v>3126789043</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>95</v>
+        <v>81</v>
       </c>
       <c r="F4" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="G4" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="G4" s="6" t="s">
-        <v>77</v>
-      </c>
       <c r="H4" s="6" t="s">
-        <v>102</v>
+        <v>88</v>
       </c>
       <c r="I4" s="6" t="s">
-        <v>122</v>
+        <v>108</v>
       </c>
       <c r="J4" s="6" t="s">
-        <v>123</v>
+        <v>109</v>
       </c>
     </row>
     <row r="5" spans="1:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>19</v>
+        <v>144</v>
       </c>
       <c r="C5" s="7">
         <v>46272</v>
@@ -1026,30 +1181,30 @@
         <v>3137890154</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>93</v>
+        <v>79</v>
       </c>
       <c r="F5" s="9" t="s">
-        <v>80</v>
+        <v>66</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>103</v>
+        <v>89</v>
       </c>
       <c r="I5" s="6" t="s">
-        <v>124</v>
+        <v>110</v>
       </c>
       <c r="J5" s="6" t="s">
-        <v>125</v>
+        <v>111</v>
       </c>
     </row>
     <row r="6" spans="1:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>22</v>
+        <v>143</v>
       </c>
       <c r="C6" s="7">
         <v>46272</v>
@@ -1058,30 +1213,30 @@
         <v>3148901265</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>92</v>
+        <v>78</v>
       </c>
       <c r="F6" s="9" t="s">
-        <v>79</v>
+        <v>65</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>104</v>
+        <v>90</v>
       </c>
       <c r="I6" s="6" t="s">
-        <v>126</v>
+        <v>112</v>
       </c>
       <c r="J6" s="6" t="s">
-        <v>127</v>
+        <v>113</v>
       </c>
     </row>
     <row r="7" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="6" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>25</v>
+        <v>152</v>
       </c>
       <c r="C7" s="7">
         <v>46272</v>
@@ -1090,30 +1245,30 @@
         <v>3159012376</v>
       </c>
       <c r="E7" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="F7" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="G7" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="H7" s="6" t="s">
         <v>91</v>
       </c>
-      <c r="F7" s="9" t="s">
-        <v>78</v>
-      </c>
-      <c r="G7" s="6" t="s">
-        <v>77</v>
-      </c>
-      <c r="H7" s="6" t="s">
-        <v>105</v>
-      </c>
       <c r="I7" s="6" t="s">
-        <v>128</v>
+        <v>114</v>
       </c>
       <c r="J7" s="6" t="s">
-        <v>129</v>
+        <v>115</v>
       </c>
     </row>
     <row r="8" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>27</v>
+        <v>142</v>
       </c>
       <c r="C8" s="7">
         <v>46272</v>
@@ -1122,30 +1277,30 @@
         <v>3160123487</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>90</v>
+        <v>76</v>
       </c>
       <c r="F8" s="9" t="s">
-        <v>67</v>
+        <v>53</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="H8" s="6" t="s">
-        <v>106</v>
+        <v>92</v>
       </c>
       <c r="I8" s="6" t="s">
-        <v>130</v>
+        <v>116</v>
       </c>
       <c r="J8" s="6" t="s">
-        <v>131</v>
+        <v>117</v>
       </c>
     </row>
     <row r="9" spans="1:10" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="C9" s="7">
         <v>46272</v>
@@ -1154,30 +1309,30 @@
         <v>3171234598</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>89</v>
+        <v>75</v>
       </c>
       <c r="F9" s="9" t="s">
-        <v>64</v>
+        <v>50</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="H9" s="6" t="s">
-        <v>107</v>
+        <v>93</v>
       </c>
       <c r="I9" s="6" t="s">
-        <v>132</v>
+        <v>118</v>
       </c>
       <c r="J9" s="6" t="s">
-        <v>133</v>
+        <v>119</v>
       </c>
     </row>
     <row r="10" spans="1:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="C10" s="7">
         <v>46272</v>
@@ -1186,30 +1341,30 @@
         <v>3182345609</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="F10" s="9" t="s">
-        <v>65</v>
+        <v>51</v>
       </c>
       <c r="G10" s="6" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="H10" s="6" t="s">
-        <v>108</v>
+        <v>94</v>
       </c>
       <c r="I10" s="6" t="s">
-        <v>134</v>
+        <v>120</v>
       </c>
       <c r="J10" s="6" t="s">
-        <v>135</v>
+        <v>121</v>
       </c>
     </row>
     <row r="11" spans="1:10" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="6" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="C11" s="7">
         <v>46272</v>
@@ -1218,30 +1373,30 @@
         <v>3193456710</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>87</v>
+        <v>73</v>
       </c>
       <c r="F11" s="9" t="s">
-        <v>66</v>
+        <v>52</v>
       </c>
       <c r="G11" s="6" t="s">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="H11" s="6" t="s">
-        <v>109</v>
+        <v>95</v>
       </c>
       <c r="I11" s="6" t="s">
-        <v>136</v>
+        <v>122</v>
       </c>
       <c r="J11" s="6" t="s">
-        <v>137</v>
+        <v>123</v>
       </c>
     </row>
     <row r="12" spans="1:10" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="6" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>38</v>
+        <v>147</v>
       </c>
       <c r="C12" s="7">
         <v>46272</v>
@@ -1250,30 +1405,30 @@
         <v>3004567821</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>86</v>
+        <v>72</v>
       </c>
       <c r="F12" s="9" t="s">
-        <v>68</v>
+        <v>54</v>
       </c>
       <c r="G12" s="6" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="H12" s="6" t="s">
-        <v>110</v>
+        <v>96</v>
       </c>
       <c r="I12" s="6" t="s">
-        <v>138</v>
+        <v>124</v>
       </c>
       <c r="J12" s="6" t="s">
-        <v>139</v>
+        <v>125</v>
       </c>
     </row>
     <row r="13" spans="1:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="6" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="C13" s="7">
         <v>46272</v>
@@ -1282,30 +1437,30 @@
         <v>3015678932</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>85</v>
+        <v>71</v>
       </c>
       <c r="F13" s="9" t="s">
-        <v>69</v>
+        <v>55</v>
       </c>
       <c r="G13" s="6" t="s">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="H13" s="6" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="I13" s="6" t="s">
-        <v>140</v>
+        <v>126</v>
       </c>
       <c r="J13" s="6" t="s">
-        <v>141</v>
+        <v>127</v>
       </c>
     </row>
     <row r="14" spans="1:10" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="6" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>44</v>
+        <v>153</v>
       </c>
       <c r="C14" s="7">
         <v>46272</v>
@@ -1314,30 +1469,30 @@
         <v>3026789043</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>84</v>
+        <v>70</v>
       </c>
       <c r="F14" s="9" t="s">
-        <v>70</v>
+        <v>56</v>
       </c>
       <c r="G14" s="6" t="s">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="H14" s="6" t="s">
-        <v>112</v>
+        <v>98</v>
       </c>
       <c r="I14" s="6" t="s">
-        <v>142</v>
+        <v>128</v>
       </c>
       <c r="J14" s="6" t="s">
-        <v>143</v>
+        <v>129</v>
       </c>
     </row>
     <row r="15" spans="1:10" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="6" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>46</v>
+        <v>148</v>
       </c>
       <c r="C15" s="7">
         <v>46272</v>
@@ -1346,30 +1501,30 @@
         <v>3037890154</v>
       </c>
       <c r="E15" s="6" t="s">
-        <v>83</v>
+        <v>69</v>
       </c>
       <c r="F15" s="9" t="s">
-        <v>71</v>
+        <v>57</v>
       </c>
       <c r="G15" s="6" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>113</v>
+        <v>99</v>
       </c>
       <c r="I15" s="6" t="s">
-        <v>144</v>
+        <v>130</v>
       </c>
       <c r="J15" s="6" t="s">
-        <v>145</v>
+        <v>131</v>
       </c>
     </row>
     <row r="16" spans="1:10" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="C16" s="7">
         <v>46272</v>
@@ -1378,30 +1533,30 @@
         <v>3048901265</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>82</v>
+        <v>68</v>
       </c>
       <c r="F16" s="9" t="s">
-        <v>72</v>
+        <v>58</v>
       </c>
       <c r="G16" s="6" t="s">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="H16" s="6" t="s">
-        <v>114</v>
+        <v>100</v>
       </c>
       <c r="I16" s="6" t="s">
-        <v>146</v>
+        <v>132</v>
       </c>
       <c r="J16" s="6" t="s">
-        <v>147</v>
+        <v>133</v>
       </c>
     </row>
     <row r="17" spans="1:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="6" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>52</v>
+        <v>149</v>
       </c>
       <c r="C17" s="7">
         <v>46272</v>
@@ -1410,30 +1565,30 @@
         <v>3059012376</v>
       </c>
       <c r="E17" s="6" t="s">
-        <v>96</v>
+        <v>82</v>
       </c>
       <c r="F17" s="9" t="s">
-        <v>73</v>
+        <v>59</v>
       </c>
       <c r="G17" s="6" t="s">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="H17" s="6" t="s">
-        <v>115</v>
+        <v>101</v>
       </c>
       <c r="I17" s="6" t="s">
-        <v>148</v>
+        <v>134</v>
       </c>
       <c r="J17" s="6" t="s">
-        <v>149</v>
+        <v>135</v>
       </c>
     </row>
     <row r="18" spans="1:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="6" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>54</v>
+        <v>150</v>
       </c>
       <c r="C18" s="7">
         <v>46272</v>
@@ -1442,30 +1597,30 @@
         <v>3060123487</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>97</v>
+        <v>83</v>
       </c>
       <c r="F18" s="9" t="s">
-        <v>74</v>
+        <v>60</v>
       </c>
       <c r="G18" s="6" t="s">
-        <v>55</v>
+        <v>28</v>
       </c>
       <c r="H18" s="6" t="s">
-        <v>116</v>
+        <v>102</v>
       </c>
       <c r="I18" s="6" t="s">
-        <v>150</v>
+        <v>136</v>
       </c>
       <c r="J18" s="6" t="s">
-        <v>151</v>
+        <v>137</v>
       </c>
     </row>
     <row r="19" spans="1:10" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="6" t="s">
-        <v>56</v>
+        <v>43</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>57</v>
+        <v>151</v>
       </c>
       <c r="C19" s="7">
         <v>46272</v>
@@ -1474,30 +1629,30 @@
         <v>3071234598</v>
       </c>
       <c r="E19" s="6" t="s">
-        <v>98</v>
+        <v>84</v>
       </c>
       <c r="F19" s="9" t="s">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="G19" s="6" t="s">
-        <v>58</v>
+        <v>44</v>
       </c>
       <c r="H19" s="6" t="s">
-        <v>105</v>
+        <v>91</v>
       </c>
       <c r="I19" s="6" t="s">
-        <v>152</v>
+        <v>138</v>
       </c>
       <c r="J19" s="6" t="s">
-        <v>153</v>
+        <v>139</v>
       </c>
     </row>
     <row r="20" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="6" t="s">
-        <v>59</v>
+        <v>45</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="C20" s="7">
         <v>46272</v>
@@ -1506,22 +1661,22 @@
         <v>3082345609</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>99</v>
+        <v>85</v>
       </c>
       <c r="F20" s="9" t="s">
-        <v>76</v>
+        <v>62</v>
       </c>
       <c r="G20" s="6" t="s">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="H20" s="6" t="s">
-        <v>117</v>
+        <v>103</v>
       </c>
       <c r="I20" s="6" t="s">
-        <v>154</v>
+        <v>140</v>
       </c>
       <c r="J20" s="6" t="s">
-        <v>155</v>
+        <v>141</v>
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.25">
@@ -1728,4 +1883,1130 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId19"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C534E5AF-0EAE-4F8B-841A-ABEE82DC078C}">
+  <dimension ref="A1:J51"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="28.7109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="29" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="38.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="43.85546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="46" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="I1" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="J1" s="5" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="19" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2" s="19" t="s">
+        <v>146</v>
+      </c>
+      <c r="C2" s="20">
+        <v>46272</v>
+      </c>
+      <c r="D2" s="19">
+        <v>3104567821</v>
+      </c>
+      <c r="E2" s="19" t="s">
+        <v>67</v>
+      </c>
+      <c r="F2" s="21" t="s">
+        <v>47</v>
+      </c>
+      <c r="G2" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="H2" s="19" t="s">
+        <v>156</v>
+      </c>
+      <c r="I2" s="19" t="s">
+        <v>161</v>
+      </c>
+      <c r="J2" s="19" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="19" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" s="19" t="s">
+        <v>146</v>
+      </c>
+      <c r="C3" s="20">
+        <v>46272</v>
+      </c>
+      <c r="D3" s="19">
+        <v>3104567821</v>
+      </c>
+      <c r="E3" s="19" t="s">
+        <v>67</v>
+      </c>
+      <c r="F3" s="21" t="s">
+        <v>47</v>
+      </c>
+      <c r="G3" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="H3" s="19" t="s">
+        <v>157</v>
+      </c>
+      <c r="I3" s="19" t="s">
+        <v>160</v>
+      </c>
+      <c r="J3" s="19" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="19" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" s="19" t="s">
+        <v>146</v>
+      </c>
+      <c r="C4" s="20">
+        <v>46272</v>
+      </c>
+      <c r="D4" s="19">
+        <v>3104567821</v>
+      </c>
+      <c r="E4" s="19" t="s">
+        <v>67</v>
+      </c>
+      <c r="F4" s="21" t="s">
+        <v>47</v>
+      </c>
+      <c r="G4" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="H4" s="19" t="s">
+        <v>158</v>
+      </c>
+      <c r="I4" s="19" t="s">
+        <v>159</v>
+      </c>
+      <c r="J4" s="19" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="16" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="C5" s="17">
+        <v>46272</v>
+      </c>
+      <c r="D5" s="16">
+        <v>3115678932</v>
+      </c>
+      <c r="E5" s="16" t="s">
+        <v>80</v>
+      </c>
+      <c r="F5" s="18" t="s">
+        <v>48</v>
+      </c>
+      <c r="G5" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="H5" s="16" t="s">
+        <v>164</v>
+      </c>
+      <c r="I5" s="16" t="s">
+        <v>167</v>
+      </c>
+      <c r="J5" s="16" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="16" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="C6" s="17">
+        <v>46272</v>
+      </c>
+      <c r="D6" s="16">
+        <v>3115678932</v>
+      </c>
+      <c r="E6" s="16" t="s">
+        <v>80</v>
+      </c>
+      <c r="F6" s="18" t="s">
+        <v>48</v>
+      </c>
+      <c r="G6" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="H6" s="16" t="s">
+        <v>165</v>
+      </c>
+      <c r="I6" s="16" t="s">
+        <v>166</v>
+      </c>
+      <c r="J6" s="16" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="B7" s="13" t="s">
+        <v>145</v>
+      </c>
+      <c r="C7" s="14">
+        <v>46272</v>
+      </c>
+      <c r="D7" s="13">
+        <v>3126789043</v>
+      </c>
+      <c r="E7" s="13" t="s">
+        <v>81</v>
+      </c>
+      <c r="F7" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="G7" s="13" t="s">
+        <v>63</v>
+      </c>
+      <c r="H7" s="13" t="s">
+        <v>170</v>
+      </c>
+      <c r="I7" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="J7" s="13" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="B8" s="13" t="s">
+        <v>145</v>
+      </c>
+      <c r="C8" s="14">
+        <v>46272</v>
+      </c>
+      <c r="D8" s="13">
+        <v>3126789043</v>
+      </c>
+      <c r="E8" s="13" t="s">
+        <v>81</v>
+      </c>
+      <c r="F8" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="G8" s="13" t="s">
+        <v>63</v>
+      </c>
+      <c r="H8" s="13" t="s">
+        <v>171</v>
+      </c>
+      <c r="I8" s="13" t="s">
+        <v>173</v>
+      </c>
+      <c r="J8" s="13" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="B9" s="13" t="s">
+        <v>145</v>
+      </c>
+      <c r="C9" s="14">
+        <v>46272</v>
+      </c>
+      <c r="D9" s="13">
+        <v>3126789043</v>
+      </c>
+      <c r="E9" s="13" t="s">
+        <v>81</v>
+      </c>
+      <c r="F9" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="G9" s="13" t="s">
+        <v>63</v>
+      </c>
+      <c r="H9" s="13" t="s">
+        <v>157</v>
+      </c>
+      <c r="I9" s="13" t="s">
+        <v>172</v>
+      </c>
+      <c r="J9" s="13" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="B10" s="10" t="s">
+        <v>154</v>
+      </c>
+      <c r="C10" s="11">
+        <v>46272</v>
+      </c>
+      <c r="D10" s="10">
+        <v>3137890154</v>
+      </c>
+      <c r="E10" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="F10" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="G10" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="H10" s="10" t="s">
+        <v>171</v>
+      </c>
+      <c r="I10" s="10" t="s">
+        <v>179</v>
+      </c>
+      <c r="J10" s="10" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="B11" s="10" t="s">
+        <v>154</v>
+      </c>
+      <c r="C11" s="11">
+        <v>46272</v>
+      </c>
+      <c r="D11" s="10">
+        <v>3137890154</v>
+      </c>
+      <c r="E11" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="F11" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="G11" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="H11" s="10" t="s">
+        <v>177</v>
+      </c>
+      <c r="I11" s="10" t="s">
+        <v>178</v>
+      </c>
+      <c r="J11" s="10" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A12" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>155</v>
+      </c>
+      <c r="C12" s="7">
+        <v>46272</v>
+      </c>
+      <c r="D12" s="6">
+        <v>3148901265</v>
+      </c>
+      <c r="E12" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="F12" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="G12" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="H12" s="6" t="s">
+        <v>158</v>
+      </c>
+      <c r="I12" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="J12" s="6" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>155</v>
+      </c>
+      <c r="C13" s="7">
+        <v>46273</v>
+      </c>
+      <c r="D13" s="6">
+        <v>3148901266</v>
+      </c>
+      <c r="E13" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="F13" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="G13" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="H13" s="6" t="s">
+        <v>183</v>
+      </c>
+      <c r="I13" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="J13" s="6" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>155</v>
+      </c>
+      <c r="C14" s="7">
+        <v>46274</v>
+      </c>
+      <c r="D14" s="6">
+        <v>3148901267</v>
+      </c>
+      <c r="E14" s="6" t="s">
+        <v>182</v>
+      </c>
+      <c r="F14" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="G14" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="H14" s="6" t="s">
+        <v>165</v>
+      </c>
+      <c r="I14" s="6" t="s">
+        <v>185</v>
+      </c>
+      <c r="J14" s="6" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>152</v>
+      </c>
+      <c r="C15" s="7">
+        <v>46272</v>
+      </c>
+      <c r="D15" s="6">
+        <v>3159012376</v>
+      </c>
+      <c r="E15" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="F15" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="G15" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="H15" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="I15" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="J15" s="6" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>142</v>
+      </c>
+      <c r="C16" s="7">
+        <v>46272</v>
+      </c>
+      <c r="D16" s="6">
+        <v>3160123487</v>
+      </c>
+      <c r="E16" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="F16" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="G16" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="H16" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="I16" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="J16" s="6" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C17" s="7">
+        <v>46272</v>
+      </c>
+      <c r="D17" s="6">
+        <v>3171234598</v>
+      </c>
+      <c r="E17" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="F17" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="G17" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="H17" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="I17" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="J17" s="6" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="C18" s="7">
+        <v>46272</v>
+      </c>
+      <c r="D18" s="6">
+        <v>3182345609</v>
+      </c>
+      <c r="E18" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="F18" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="G18" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="H18" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="I18" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="J18" s="6" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="C19" s="7">
+        <v>46272</v>
+      </c>
+      <c r="D19" s="6">
+        <v>3193456710</v>
+      </c>
+      <c r="E19" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="F19" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="G19" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="H19" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="I19" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="J19" s="6" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="B20" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="C20" s="7">
+        <v>46272</v>
+      </c>
+      <c r="D20" s="6">
+        <v>3004567821</v>
+      </c>
+      <c r="E20" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="F20" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="G20" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="H20" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="I20" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="J20" s="6" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="B21" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="C21" s="7">
+        <v>46272</v>
+      </c>
+      <c r="D21" s="6">
+        <v>3015678932</v>
+      </c>
+      <c r="E21" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="F21" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="G21" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="H21" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="I21" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="J21" s="6" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="B22" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="C22" s="7">
+        <v>46272</v>
+      </c>
+      <c r="D22" s="6">
+        <v>3026789043</v>
+      </c>
+      <c r="E22" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="F22" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="G22" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="H22" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="I22" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="J22" s="6" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="B23" s="6" t="s">
+        <v>148</v>
+      </c>
+      <c r="C23" s="7">
+        <v>46272</v>
+      </c>
+      <c r="D23" s="6">
+        <v>3037890154</v>
+      </c>
+      <c r="E23" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="F23" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="G23" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="H23" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="I23" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="J23" s="6" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B24" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="C24" s="7">
+        <v>46272</v>
+      </c>
+      <c r="D24" s="6">
+        <v>3048901265</v>
+      </c>
+      <c r="E24" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="F24" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="G24" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="H24" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="I24" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="J24" s="6" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B25" s="6" t="s">
+        <v>149</v>
+      </c>
+      <c r="C25" s="7">
+        <v>46272</v>
+      </c>
+      <c r="D25" s="6">
+        <v>3059012376</v>
+      </c>
+      <c r="E25" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="F25" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="G25" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="H25" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="I25" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="J25" s="6" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B26" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="C26" s="7">
+        <v>46272</v>
+      </c>
+      <c r="D26" s="6">
+        <v>3060123487</v>
+      </c>
+      <c r="E26" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="F26" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="G26" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="H26" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="I26" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="J26" s="6" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B27" s="6" t="s">
+        <v>151</v>
+      </c>
+      <c r="C27" s="7">
+        <v>46272</v>
+      </c>
+      <c r="D27" s="6">
+        <v>3071234598</v>
+      </c>
+      <c r="E27" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="F27" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="G27" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="H27" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="I27" s="6" t="s">
+        <v>138</v>
+      </c>
+      <c r="J27" s="6" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B28" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="C28" s="7">
+        <v>46272</v>
+      </c>
+      <c r="D28" s="6">
+        <v>3082345609</v>
+      </c>
+      <c r="E28" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="F28" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="G28" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="H28" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="I28" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="J28" s="6" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A32" s="1"/>
+      <c r="B32" s="1"/>
+      <c r="C32" s="1"/>
+      <c r="D32" s="1"/>
+      <c r="E32" s="1"/>
+      <c r="F32" s="1"/>
+      <c r="G32" s="1"/>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A33" s="2"/>
+      <c r="B33" s="2"/>
+      <c r="C33" s="3"/>
+      <c r="D33" s="2"/>
+      <c r="E33" s="2"/>
+      <c r="F33" s="4"/>
+      <c r="G33" s="2"/>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A34" s="2"/>
+      <c r="B34" s="2"/>
+      <c r="C34" s="3"/>
+      <c r="D34" s="2"/>
+      <c r="E34" s="2"/>
+      <c r="F34" s="4"/>
+      <c r="G34" s="2"/>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A35" s="2"/>
+      <c r="B35" s="2"/>
+      <c r="C35" s="3"/>
+      <c r="D35" s="2"/>
+      <c r="E35" s="2"/>
+      <c r="F35" s="4"/>
+      <c r="G35" s="2"/>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A36" s="2"/>
+      <c r="B36" s="2"/>
+      <c r="C36" s="3"/>
+      <c r="D36" s="2"/>
+      <c r="E36" s="2"/>
+      <c r="F36" s="4"/>
+      <c r="G36" s="2"/>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A37" s="2"/>
+      <c r="B37" s="2"/>
+      <c r="C37" s="3"/>
+      <c r="D37" s="2"/>
+      <c r="E37" s="2"/>
+      <c r="F37" s="4"/>
+      <c r="G37" s="2"/>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A38" s="2"/>
+      <c r="B38" s="2"/>
+      <c r="C38" s="3"/>
+      <c r="D38" s="2"/>
+      <c r="E38" s="2"/>
+      <c r="F38" s="4"/>
+      <c r="G38" s="2"/>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A39" s="2"/>
+      <c r="B39" s="2"/>
+      <c r="C39" s="3"/>
+      <c r="D39" s="2"/>
+      <c r="E39" s="2"/>
+      <c r="F39" s="4"/>
+      <c r="G39" s="2"/>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A40" s="2"/>
+      <c r="B40" s="2"/>
+      <c r="C40" s="3"/>
+      <c r="D40" s="2"/>
+      <c r="E40" s="2"/>
+      <c r="F40" s="4"/>
+      <c r="G40" s="2"/>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A41" s="2"/>
+      <c r="B41" s="2"/>
+      <c r="C41" s="3"/>
+      <c r="D41" s="2"/>
+      <c r="E41" s="2"/>
+      <c r="F41" s="4"/>
+      <c r="G41" s="2"/>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A42" s="2"/>
+      <c r="B42" s="2"/>
+      <c r="C42" s="3"/>
+      <c r="D42" s="2"/>
+      <c r="E42" s="2"/>
+      <c r="F42" s="4"/>
+      <c r="G42" s="2"/>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A43" s="2"/>
+      <c r="B43" s="2"/>
+      <c r="C43" s="3"/>
+      <c r="D43" s="2"/>
+      <c r="E43" s="2"/>
+      <c r="F43" s="4"/>
+      <c r="G43" s="2"/>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A44" s="2"/>
+      <c r="B44" s="2"/>
+      <c r="C44" s="3"/>
+      <c r="D44" s="2"/>
+      <c r="E44" s="2"/>
+      <c r="F44" s="4"/>
+      <c r="G44" s="2"/>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A45" s="2"/>
+      <c r="B45" s="2"/>
+      <c r="C45" s="3"/>
+      <c r="D45" s="2"/>
+      <c r="E45" s="2"/>
+      <c r="F45" s="4"/>
+      <c r="G45" s="2"/>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A46" s="2"/>
+      <c r="B46" s="2"/>
+      <c r="C46" s="3"/>
+      <c r="D46" s="2"/>
+      <c r="E46" s="2"/>
+      <c r="F46" s="4"/>
+      <c r="G46" s="2"/>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A47" s="2"/>
+      <c r="B47" s="2"/>
+      <c r="C47" s="3"/>
+      <c r="D47" s="2"/>
+      <c r="E47" s="2"/>
+      <c r="F47" s="4"/>
+      <c r="G47" s="2"/>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A48" s="2"/>
+      <c r="B48" s="2"/>
+      <c r="C48" s="3"/>
+      <c r="D48" s="2"/>
+      <c r="E48" s="2"/>
+      <c r="F48" s="4"/>
+      <c r="G48" s="2"/>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A49" s="2"/>
+      <c r="B49" s="2"/>
+      <c r="C49" s="3"/>
+      <c r="D49" s="2"/>
+      <c r="E49" s="2"/>
+      <c r="F49" s="4"/>
+      <c r="G49" s="2"/>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A50" s="2"/>
+      <c r="B50" s="2"/>
+      <c r="C50" s="3"/>
+      <c r="D50" s="2"/>
+      <c r="E50" s="2"/>
+      <c r="F50" s="4"/>
+      <c r="G50" s="2"/>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A51" s="2"/>
+      <c r="B51" s="2"/>
+      <c r="C51" s="3"/>
+      <c r="D51" s="2"/>
+      <c r="E51" s="2"/>
+      <c r="F51" s="4"/>
+      <c r="G51" s="2"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
+  <hyperlinks>
+    <hyperlink ref="F6" r:id="rId1" xr:uid="{6326BC65-0AC6-40CF-A76D-14B409E0134B}"/>
+    <hyperlink ref="F9" r:id="rId2" xr:uid="{D88A0B46-DBA1-4568-ABBB-E1A890937830}"/>
+    <hyperlink ref="F17" r:id="rId3" xr:uid="{A51E2D82-DF9B-46D7-B79B-E43BC71EADBE}"/>
+    <hyperlink ref="F18" r:id="rId4" xr:uid="{E072F17F-AF51-4AE5-8A7F-A13CA911E563}"/>
+    <hyperlink ref="F19" r:id="rId5" xr:uid="{58EA014F-D83F-48BF-BADE-67BCA9BEF585}"/>
+    <hyperlink ref="F16" r:id="rId6" xr:uid="{8AD8FC03-429B-4FD7-BDF7-82BE8D4E6337}"/>
+    <hyperlink ref="F20" r:id="rId7" xr:uid="{75B1B474-E684-4161-B983-6A2F6CCA185A}"/>
+    <hyperlink ref="F21" r:id="rId8" xr:uid="{40E30AD9-BEDA-4A27-8BDE-158EC7180ECE}"/>
+    <hyperlink ref="F22" r:id="rId9" xr:uid="{BE08C16A-4E93-406A-BA0B-35B62ABEC2AA}"/>
+    <hyperlink ref="F23" r:id="rId10" xr:uid="{E2524138-4615-462E-8D0A-04B1773291D0}"/>
+    <hyperlink ref="F24" r:id="rId11" xr:uid="{08F09F79-8731-44B5-93EF-9E082C4F2254}"/>
+    <hyperlink ref="F25" r:id="rId12" xr:uid="{D272E36F-85B9-4196-8BF0-8D3EF050FABB}"/>
+    <hyperlink ref="F26" r:id="rId13" xr:uid="{E509F268-7FCA-43E2-9480-12E9C0B1E001}"/>
+    <hyperlink ref="F27" r:id="rId14" xr:uid="{650D3E9E-C3B8-4380-B4E6-05224EB62ECD}"/>
+    <hyperlink ref="F28" r:id="rId15" xr:uid="{95EAB623-BDE2-4053-8CF4-C4F073C0B5CD}"/>
+    <hyperlink ref="F15" r:id="rId16" xr:uid="{D5703FBC-EB8E-4E88-A312-6AE225A408E7}"/>
+    <hyperlink ref="F12" r:id="rId17" xr:uid="{A62E5892-D8AA-4021-95C3-56FD52B8C8F9}"/>
+    <hyperlink ref="F11" r:id="rId18" xr:uid="{14893CA0-E2B4-4AA4-997B-4120BDEE235B}"/>
+    <hyperlink ref="F5" r:id="rId19" xr:uid="{8A817A38-CE90-4F54-8E74-CC7CDF635018}"/>
+    <hyperlink ref="F7" r:id="rId20" xr:uid="{8D7973DE-BDDE-4706-87C1-B11912E6CE19}"/>
+    <hyperlink ref="F8" r:id="rId21" xr:uid="{C2BF9E1C-E71A-4713-A3BA-2E73D4517902}"/>
+    <hyperlink ref="F10" r:id="rId22" xr:uid="{5CA48F6C-8D9E-47C3-AB82-E1B408B4F7C4}"/>
+    <hyperlink ref="F13" r:id="rId23" xr:uid="{7641A20B-8D54-402B-B9B9-A87B8C48DCFA}"/>
+    <hyperlink ref="F14" r:id="rId24" xr:uid="{60C28499-7AC6-493A-A69E-96EE88713BA4}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId25"/>
+</worksheet>
 </file>
--- a/ComponentesMetodologicos/Normalizacion.xlsx
+++ b/ComponentesMetodologicos/Normalizacion.xlsx
@@ -8,13 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GABRIEL\PROYECTO_CEREBRUM\ComponentesMetodologicos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0AE4DB61-32B0-4EE7-97C4-A7C72E626100}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6AA5C378-4CDC-4224-A571-4D9E5AFD9877}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
     <sheet name="1FN" sheetId="2" r:id="rId2"/>
+    <sheet name="2FN" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -26,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="388" uniqueCount="189">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="966" uniqueCount="225">
   <si>
     <t>Cuenta</t>
   </si>
@@ -593,6 +594,114 @@
   </si>
   <si>
     <t>Idea principal</t>
+  </si>
+  <si>
+    <t>Reacciones químicas</t>
+  </si>
+  <si>
+    <t>Fuerzas</t>
+  </si>
+  <si>
+    <t>Leyes de Newton</t>
+  </si>
+  <si>
+    <t>Balanceo de ecuaciones</t>
+  </si>
+  <si>
+    <t>Seno y coseno</t>
+  </si>
+  <si>
+    <t>Vida cotidiana</t>
+  </si>
+  <si>
+    <t>Aceleración</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Inglés</t>
+  </si>
+  <si>
+    <t>Trigonometría</t>
+  </si>
+  <si>
+    <t>Vocabulario</t>
+  </si>
+  <si>
+    <t>Movimiento</t>
+  </si>
+  <si>
+    <t>Colombia</t>
+  </si>
+  <si>
+    <t>Independencia</t>
+  </si>
+  <si>
+    <t>Programación</t>
+  </si>
+  <si>
+    <t>Algoritmos</t>
+  </si>
+  <si>
+    <t>Energía</t>
+  </si>
+  <si>
+    <t>Energía cinética</t>
+  </si>
+  <si>
+    <t>Ecuaciones</t>
+  </si>
+  <si>
+    <t>Condicionales</t>
+  </si>
+  <si>
+    <t>Tabla periódica</t>
+  </si>
+  <si>
+    <t>Ecología</t>
+  </si>
+  <si>
+    <t>Ecosistemas</t>
+  </si>
+  <si>
+    <t>Tiempos verbales</t>
+  </si>
+  <si>
+    <t>Grupos y períodos</t>
+  </si>
+  <si>
+    <t>Triángulos</t>
+  </si>
+  <si>
+    <t>Constitución</t>
+  </si>
+  <si>
+    <t>Propiedades</t>
+  </si>
+  <si>
+    <t>Argumentación</t>
+  </si>
+  <si>
+    <t>Biología,</t>
+  </si>
+  <si>
+    <t>Tesis</t>
+  </si>
+  <si>
+    <t>Comprensión lectora</t>
+  </si>
+  <si>
+    <t>Verbos</t>
+  </si>
+  <si>
+    <t>Edad Moderna</t>
+  </si>
+  <si>
+    <t>Balanceo</t>
+  </si>
+  <si>
+    <t>Probabilidad</t>
+  </si>
+  <si>
+    <t>Eventos</t>
   </si>
 </sst>
 </file>
@@ -630,7 +739,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="16">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -658,6 +767,66 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="3" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2" tint="-9.9978637043366805E-2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B0F0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCCFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.249977111117893"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -690,7 +859,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="53">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -743,6 +912,77 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="1" xfId="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="1" xfId="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="1" xfId="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="12" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="1" xfId="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="13" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="1" xfId="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="14" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="14" borderId="1" xfId="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="15" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="15" borderId="1" xfId="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -750,6 +990,11 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="FFFFCCFF"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -1887,7 +2132,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C534E5AF-0EAE-4F8B-841A-ABEE82DC078C}">
-  <dimension ref="A1:J51"/>
+  <dimension ref="A1:J73"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7.28515625" bestFit="1" customWidth="1"/>
@@ -1897,9 +2142,9 @@
     <col min="5" max="5" width="15.5703125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="28.7109375" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="29" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="38.42578125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="43.85546875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="46" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="20" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="22.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -1934,7 +2179,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="19" t="s">
         <v>10</v>
       </c>
@@ -1963,10 +2208,10 @@
         <v>161</v>
       </c>
       <c r="J2" s="19" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="19" t="s">
         <v>10</v>
       </c>
@@ -1998,7 +2243,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="4" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="19" t="s">
         <v>10</v>
       </c>
@@ -2030,7 +2275,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="5" spans="1:10" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="16" t="s">
         <v>12</v>
       </c>
@@ -2062,7 +2307,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="6" spans="1:10" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="16" t="s">
         <v>12</v>
       </c>
@@ -2094,7 +2339,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="7" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="13" t="s">
         <v>15</v>
       </c>
@@ -2126,7 +2371,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="8" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" s="13" t="s">
         <v>15</v>
       </c>
@@ -2158,7 +2403,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="9" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="13" t="s">
         <v>15</v>
       </c>
@@ -2190,7 +2435,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="10" spans="1:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="10" t="s">
         <v>16</v>
       </c>
@@ -2222,7 +2467,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="11" spans="1:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" s="10" t="s">
         <v>16</v>
       </c>
@@ -2255,747 +2500,1451 @@
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A12" s="6" t="s">
+      <c r="A12" s="22" t="s">
         <v>18</v>
       </c>
-      <c r="B12" s="6" t="s">
+      <c r="B12" s="22" t="s">
         <v>155</v>
       </c>
-      <c r="C12" s="7">
-        <v>46272</v>
-      </c>
-      <c r="D12" s="6">
+      <c r="C12" s="23">
+        <v>46272</v>
+      </c>
+      <c r="D12" s="22">
         <v>3148901265</v>
       </c>
-      <c r="E12" s="6" t="s">
+      <c r="E12" s="22" t="s">
         <v>78</v>
       </c>
-      <c r="F12" s="9" t="s">
+      <c r="F12" s="24" t="s">
         <v>65</v>
       </c>
-      <c r="G12" s="6" t="s">
+      <c r="G12" s="22" t="s">
         <v>19</v>
       </c>
-      <c r="H12" s="6" t="s">
+      <c r="H12" s="22" t="s">
         <v>158</v>
       </c>
-      <c r="I12" s="6" t="s">
+      <c r="I12" s="22" t="s">
         <v>159</v>
       </c>
-      <c r="J12" s="6" t="s">
+      <c r="J12" s="22" t="s">
         <v>187</v>
       </c>
     </row>
-    <row r="13" spans="1:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="6" t="s">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A13" s="22" t="s">
         <v>18</v>
       </c>
-      <c r="B13" s="6" t="s">
+      <c r="B13" s="22" t="s">
         <v>155</v>
       </c>
-      <c r="C13" s="7">
+      <c r="C13" s="23">
         <v>46273</v>
       </c>
-      <c r="D13" s="6">
+      <c r="D13" s="22">
         <v>3148901266</v>
       </c>
-      <c r="E13" s="6" t="s">
+      <c r="E13" s="22" t="s">
         <v>77</v>
       </c>
-      <c r="F13" s="9" t="s">
+      <c r="F13" s="24" t="s">
         <v>65</v>
       </c>
-      <c r="G13" s="6" t="s">
+      <c r="G13" s="22" t="s">
         <v>19</v>
       </c>
-      <c r="H13" s="6" t="s">
+      <c r="H13" s="22" t="s">
         <v>183</v>
       </c>
-      <c r="I13" s="6" t="s">
+      <c r="I13" s="22" t="s">
         <v>184</v>
       </c>
-      <c r="J13" s="6" t="s">
+      <c r="J13" s="22" t="s">
         <v>188</v>
       </c>
     </row>
-    <row r="14" spans="1:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="6" t="s">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A14" s="22" t="s">
         <v>18</v>
       </c>
-      <c r="B14" s="6" t="s">
+      <c r="B14" s="22" t="s">
         <v>155</v>
       </c>
-      <c r="C14" s="7">
+      <c r="C14" s="23">
         <v>46274</v>
       </c>
-      <c r="D14" s="6">
+      <c r="D14" s="22">
         <v>3148901267</v>
       </c>
-      <c r="E14" s="6" t="s">
+      <c r="E14" s="22" t="s">
         <v>182</v>
       </c>
-      <c r="F14" s="9" t="s">
+      <c r="F14" s="24" t="s">
         <v>65</v>
       </c>
-      <c r="G14" s="6" t="s">
+      <c r="G14" s="22" t="s">
         <v>19</v>
       </c>
-      <c r="H14" s="6" t="s">
+      <c r="H14" s="22" t="s">
         <v>165</v>
       </c>
-      <c r="I14" s="6" t="s">
+      <c r="I14" s="22" t="s">
         <v>185</v>
       </c>
-      <c r="J14" s="6" t="s">
+      <c r="J14" s="22" t="s">
         <v>186</v>
       </c>
     </row>
-    <row r="15" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="6" t="s">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A15" s="25" t="s">
         <v>20</v>
       </c>
-      <c r="B15" s="6" t="s">
+      <c r="B15" s="25" t="s">
         <v>152</v>
       </c>
-      <c r="C15" s="7">
-        <v>46272</v>
-      </c>
-      <c r="D15" s="6">
+      <c r="C15" s="26">
+        <v>46272</v>
+      </c>
+      <c r="D15" s="25">
         <v>3159012376</v>
       </c>
-      <c r="E15" s="6" t="s">
+      <c r="E15" s="25" t="s">
         <v>77</v>
       </c>
-      <c r="F15" s="9" t="s">
+      <c r="F15" s="27" t="s">
         <v>64</v>
       </c>
-      <c r="G15" s="6" t="s">
+      <c r="G15" s="25" t="s">
         <v>63</v>
       </c>
-      <c r="H15" s="6" t="s">
-        <v>91</v>
-      </c>
-      <c r="I15" s="6" t="s">
-        <v>114</v>
-      </c>
-      <c r="J15" s="6" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="6" t="s">
+      <c r="H15" s="25" t="s">
+        <v>157</v>
+      </c>
+      <c r="I15" s="25" t="s">
+        <v>190</v>
+      </c>
+      <c r="J15" s="25" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A16" s="25" t="s">
+        <v>20</v>
+      </c>
+      <c r="B16" s="25" t="s">
+        <v>152</v>
+      </c>
+      <c r="C16" s="26">
+        <v>46272</v>
+      </c>
+      <c r="D16" s="25">
+        <v>3159012376</v>
+      </c>
+      <c r="E16" s="25" t="s">
+        <v>77</v>
+      </c>
+      <c r="F16" s="27" t="s">
+        <v>64</v>
+      </c>
+      <c r="G16" s="25" t="s">
+        <v>63</v>
+      </c>
+      <c r="H16" s="25" t="s">
+        <v>170</v>
+      </c>
+      <c r="I16" s="25" t="s">
+        <v>189</v>
+      </c>
+      <c r="J16" s="25" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A17" s="28" t="s">
         <v>21</v>
       </c>
-      <c r="B16" s="6" t="s">
+      <c r="B17" s="28" t="s">
         <v>142</v>
       </c>
-      <c r="C16" s="7">
-        <v>46272</v>
-      </c>
-      <c r="D16" s="6">
+      <c r="C17" s="29">
+        <v>46272</v>
+      </c>
+      <c r="D17" s="28">
         <v>3160123487</v>
       </c>
-      <c r="E16" s="6" t="s">
+      <c r="E17" s="28" t="s">
         <v>76</v>
       </c>
-      <c r="F16" s="9" t="s">
+      <c r="F17" s="30" t="s">
         <v>53</v>
       </c>
-      <c r="G16" s="6" t="s">
+      <c r="G17" s="28" t="s">
         <v>22</v>
       </c>
-      <c r="H16" s="6" t="s">
-        <v>92</v>
-      </c>
-      <c r="I16" s="6" t="s">
-        <v>116</v>
-      </c>
-      <c r="J16" s="6" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="6" t="s">
+      <c r="H17" s="28" t="s">
+        <v>171</v>
+      </c>
+      <c r="I17" s="28" t="s">
+        <v>197</v>
+      </c>
+      <c r="J17" s="28" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A18" s="28" t="s">
+        <v>21</v>
+      </c>
+      <c r="B18" s="28" t="s">
+        <v>142</v>
+      </c>
+      <c r="C18" s="29">
+        <v>46272</v>
+      </c>
+      <c r="D18" s="28">
+        <v>3160123487</v>
+      </c>
+      <c r="E18" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="F18" s="30" t="s">
+        <v>53</v>
+      </c>
+      <c r="G18" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="H18" s="28" t="s">
+        <v>196</v>
+      </c>
+      <c r="I18" s="28" t="s">
+        <v>198</v>
+      </c>
+      <c r="J18" s="28" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A19" s="28" t="s">
+        <v>21</v>
+      </c>
+      <c r="B19" s="28" t="s">
+        <v>142</v>
+      </c>
+      <c r="C19" s="29">
+        <v>46272</v>
+      </c>
+      <c r="D19" s="28">
+        <v>3160123487</v>
+      </c>
+      <c r="E19" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="F19" s="30" t="s">
+        <v>53</v>
+      </c>
+      <c r="G19" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="H19" s="28" t="s">
+        <v>157</v>
+      </c>
+      <c r="I19" s="28" t="s">
+        <v>199</v>
+      </c>
+      <c r="J19" s="28" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A20" s="31" t="s">
         <v>23</v>
       </c>
-      <c r="B17" s="6" t="s">
+      <c r="B20" s="31" t="s">
         <v>24</v>
       </c>
-      <c r="C17" s="7">
-        <v>46272</v>
-      </c>
-      <c r="D17" s="6">
+      <c r="C20" s="32">
+        <v>46272</v>
+      </c>
+      <c r="D20" s="31">
         <v>3171234598</v>
       </c>
-      <c r="E17" s="6" t="s">
+      <c r="E20" s="31" t="s">
         <v>75</v>
       </c>
-      <c r="F17" s="9" t="s">
+      <c r="F20" s="33" t="s">
         <v>50</v>
       </c>
-      <c r="G17" s="6" t="s">
+      <c r="G20" s="31" t="s">
         <v>25</v>
       </c>
-      <c r="H17" s="6" t="s">
-        <v>93</v>
-      </c>
-      <c r="I17" s="6" t="s">
-        <v>118</v>
-      </c>
-      <c r="J17" s="6" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="6" t="s">
+      <c r="H20" s="31" t="s">
+        <v>165</v>
+      </c>
+      <c r="I20" s="31" t="s">
+        <v>200</v>
+      </c>
+      <c r="J20" s="31" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A21" s="31" t="s">
+        <v>23</v>
+      </c>
+      <c r="B21" s="31" t="s">
+        <v>24</v>
+      </c>
+      <c r="C21" s="32">
+        <v>46272</v>
+      </c>
+      <c r="D21" s="31">
+        <v>3171234598</v>
+      </c>
+      <c r="E21" s="31" t="s">
+        <v>75</v>
+      </c>
+      <c r="F21" s="33" t="s">
+        <v>50</v>
+      </c>
+      <c r="G21" s="31" t="s">
+        <v>25</v>
+      </c>
+      <c r="H21" s="31" t="s">
+        <v>183</v>
+      </c>
+      <c r="I21" s="31" t="s">
+        <v>167</v>
+      </c>
+      <c r="J21" s="31" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A22" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="B18" s="6" t="s">
+      <c r="B22" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C18" s="7">
-        <v>46272</v>
-      </c>
-      <c r="D18" s="6">
+      <c r="C22" s="14">
+        <v>46272</v>
+      </c>
+      <c r="D22" s="13">
         <v>3182345609</v>
       </c>
-      <c r="E18" s="6" t="s">
+      <c r="E22" s="13" t="s">
         <v>74</v>
       </c>
-      <c r="F18" s="9" t="s">
+      <c r="F22" s="15" t="s">
         <v>51</v>
       </c>
-      <c r="G18" s="6" t="s">
+      <c r="G22" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="H18" s="6" t="s">
-        <v>94</v>
-      </c>
-      <c r="I18" s="6" t="s">
-        <v>120</v>
-      </c>
-      <c r="J18" s="6" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="6" t="s">
+      <c r="H22" s="13" t="s">
+        <v>202</v>
+      </c>
+      <c r="I22" s="13" t="s">
+        <v>203</v>
+      </c>
+      <c r="J22" s="13" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A23" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="B23" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="C23" s="14">
+        <v>46272</v>
+      </c>
+      <c r="D23" s="13">
+        <v>3182345609</v>
+      </c>
+      <c r="E23" s="13" t="s">
+        <v>74</v>
+      </c>
+      <c r="F23" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="G23" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="H23" s="13" t="s">
+        <v>171</v>
+      </c>
+      <c r="I23" s="13" t="s">
+        <v>161</v>
+      </c>
+      <c r="J23" s="13" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A24" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="B24" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="C24" s="14">
+        <v>46272</v>
+      </c>
+      <c r="D24" s="13">
+        <v>3182345609</v>
+      </c>
+      <c r="E24" s="13" t="s">
+        <v>74</v>
+      </c>
+      <c r="F24" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="G24" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="H24" s="13" t="s">
+        <v>157</v>
+      </c>
+      <c r="I24" s="13" t="s">
+        <v>204</v>
+      </c>
+      <c r="J24" s="13" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A25" s="16" t="s">
         <v>29</v>
       </c>
-      <c r="B19" s="6" t="s">
+      <c r="B25" s="16" t="s">
         <v>30</v>
       </c>
-      <c r="C19" s="7">
-        <v>46272</v>
-      </c>
-      <c r="D19" s="6">
+      <c r="C25" s="17">
+        <v>46272</v>
+      </c>
+      <c r="D25" s="16">
         <v>3193456710</v>
       </c>
-      <c r="E19" s="6" t="s">
+      <c r="E25" s="16" t="s">
         <v>73</v>
       </c>
-      <c r="F19" s="9" t="s">
+      <c r="F25" s="18" t="s">
         <v>52</v>
       </c>
-      <c r="G19" s="6" t="s">
+      <c r="G25" s="16" t="s">
         <v>63</v>
       </c>
-      <c r="H19" s="6" t="s">
-        <v>95</v>
-      </c>
-      <c r="I19" s="6" t="s">
-        <v>122</v>
-      </c>
-      <c r="J19" s="6" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="6" t="s">
+      <c r="H25" s="16" t="s">
+        <v>170</v>
+      </c>
+      <c r="I25" s="16" t="s">
+        <v>208</v>
+      </c>
+      <c r="J25" s="16" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A26" s="16" t="s">
+        <v>29</v>
+      </c>
+      <c r="B26" s="16" t="s">
+        <v>30</v>
+      </c>
+      <c r="C26" s="17">
+        <v>46272</v>
+      </c>
+      <c r="D26" s="16">
+        <v>3193456710</v>
+      </c>
+      <c r="E26" s="16" t="s">
+        <v>73</v>
+      </c>
+      <c r="F26" s="18" t="s">
+        <v>52</v>
+      </c>
+      <c r="G26" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="H26" s="16" t="s">
+        <v>158</v>
+      </c>
+      <c r="I26" s="16" t="s">
+        <v>159</v>
+      </c>
+      <c r="J26" s="16" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A27" s="16" t="s">
+        <v>29</v>
+      </c>
+      <c r="B27" s="16" t="s">
+        <v>30</v>
+      </c>
+      <c r="C27" s="17">
+        <v>46272</v>
+      </c>
+      <c r="D27" s="16">
+        <v>3193456710</v>
+      </c>
+      <c r="E27" s="16" t="s">
+        <v>73</v>
+      </c>
+      <c r="F27" s="18" t="s">
+        <v>52</v>
+      </c>
+      <c r="G27" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="H27" s="16" t="s">
+        <v>177</v>
+      </c>
+      <c r="I27" s="16" t="s">
+        <v>209</v>
+      </c>
+      <c r="J27" s="16" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A28" s="31" t="s">
         <v>31</v>
       </c>
-      <c r="B20" s="6" t="s">
+      <c r="B28" s="31" t="s">
         <v>147</v>
       </c>
-      <c r="C20" s="7">
-        <v>46272</v>
-      </c>
-      <c r="D20" s="6">
+      <c r="C28" s="32">
+        <v>46272</v>
+      </c>
+      <c r="D28" s="31">
         <v>3004567821</v>
       </c>
-      <c r="E20" s="6" t="s">
+      <c r="E28" s="31" t="s">
         <v>72</v>
       </c>
-      <c r="F20" s="9" t="s">
+      <c r="F28" s="33" t="s">
         <v>54</v>
       </c>
-      <c r="G20" s="6" t="s">
+      <c r="G28" s="31" t="s">
         <v>32</v>
       </c>
-      <c r="H20" s="6" t="s">
-        <v>96</v>
-      </c>
-      <c r="I20" s="6" t="s">
-        <v>124</v>
-      </c>
-      <c r="J20" s="6" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="6" t="s">
+      <c r="H28" s="31" t="s">
+        <v>157</v>
+      </c>
+      <c r="I28" s="31" t="s">
+        <v>190</v>
+      </c>
+      <c r="J28" s="31" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A29" s="31" t="s">
+        <v>31</v>
+      </c>
+      <c r="B29" s="31" t="s">
+        <v>147</v>
+      </c>
+      <c r="C29" s="32">
+        <v>46272</v>
+      </c>
+      <c r="D29" s="31">
+        <v>3004567821</v>
+      </c>
+      <c r="E29" s="31" t="s">
+        <v>72</v>
+      </c>
+      <c r="F29" s="33" t="s">
+        <v>54</v>
+      </c>
+      <c r="G29" s="31" t="s">
+        <v>32</v>
+      </c>
+      <c r="H29" s="31" t="s">
+        <v>171</v>
+      </c>
+      <c r="I29" s="31" t="s">
+        <v>173</v>
+      </c>
+      <c r="J29" s="31" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A30" s="34" t="s">
         <v>33</v>
       </c>
-      <c r="B21" s="6" t="s">
+      <c r="B30" s="34" t="s">
         <v>34</v>
       </c>
-      <c r="C21" s="7">
-        <v>46272</v>
-      </c>
-      <c r="D21" s="6">
+      <c r="C30" s="35">
+        <v>46272</v>
+      </c>
+      <c r="D30" s="34">
         <v>3015678932</v>
       </c>
-      <c r="E21" s="6" t="s">
+      <c r="E30" s="34" t="s">
         <v>71</v>
       </c>
-      <c r="F21" s="9" t="s">
+      <c r="F30" s="36" t="s">
         <v>55</v>
       </c>
-      <c r="G21" s="6" t="s">
+      <c r="G30" s="34" t="s">
         <v>28</v>
       </c>
-      <c r="H21" s="6" t="s">
-        <v>97</v>
-      </c>
-      <c r="I21" s="6" t="s">
-        <v>126</v>
-      </c>
-      <c r="J21" s="6" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="6" t="s">
+      <c r="H30" s="34" t="s">
+        <v>171</v>
+      </c>
+      <c r="I30" s="34" t="s">
+        <v>197</v>
+      </c>
+      <c r="J30" s="34" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A31" s="34" t="s">
+        <v>33</v>
+      </c>
+      <c r="B31" s="34" t="s">
+        <v>34</v>
+      </c>
+      <c r="C31" s="35">
+        <v>46272</v>
+      </c>
+      <c r="D31" s="34">
+        <v>3015678932</v>
+      </c>
+      <c r="E31" s="34" t="s">
+        <v>71</v>
+      </c>
+      <c r="F31" s="36" t="s">
+        <v>55</v>
+      </c>
+      <c r="G31" s="34" t="s">
+        <v>28</v>
+      </c>
+      <c r="H31" s="34" t="s">
+        <v>170</v>
+      </c>
+      <c r="I31" s="34" t="s">
+        <v>6</v>
+      </c>
+      <c r="J31" s="34" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A32" s="34" t="s">
+        <v>33</v>
+      </c>
+      <c r="B32" s="34" t="s">
+        <v>34</v>
+      </c>
+      <c r="C32" s="35">
+        <v>46272</v>
+      </c>
+      <c r="D32" s="34">
+        <v>3015678932</v>
+      </c>
+      <c r="E32" s="34" t="s">
+        <v>71</v>
+      </c>
+      <c r="F32" s="36" t="s">
+        <v>55</v>
+      </c>
+      <c r="G32" s="34" t="s">
+        <v>28</v>
+      </c>
+      <c r="H32" s="34" t="s">
+        <v>165</v>
+      </c>
+      <c r="I32" s="34" t="s">
+        <v>200</v>
+      </c>
+      <c r="J32" s="34" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A33" s="37" t="s">
         <v>35</v>
       </c>
-      <c r="B22" s="6" t="s">
+      <c r="B33" s="37" t="s">
         <v>153</v>
       </c>
-      <c r="C22" s="7">
-        <v>46272</v>
-      </c>
-      <c r="D22" s="6">
+      <c r="C33" s="38">
+        <v>46272</v>
+      </c>
+      <c r="D33" s="37">
         <v>3026789043</v>
       </c>
-      <c r="E22" s="6" t="s">
+      <c r="E33" s="37" t="s">
         <v>70</v>
       </c>
-      <c r="F22" s="9" t="s">
+      <c r="F33" s="39" t="s">
         <v>56</v>
       </c>
-      <c r="G22" s="6" t="s">
+      <c r="G33" s="37" t="s">
         <v>63</v>
       </c>
-      <c r="H22" s="6" t="s">
-        <v>98</v>
-      </c>
-      <c r="I22" s="6" t="s">
-        <v>128</v>
-      </c>
-      <c r="J22" s="6" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="6" t="s">
+      <c r="H33" s="37" t="s">
+        <v>158</v>
+      </c>
+      <c r="I33" s="37" t="s">
+        <v>198</v>
+      </c>
+      <c r="J33" s="37" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A34" s="37" t="s">
+        <v>35</v>
+      </c>
+      <c r="B34" s="37" t="s">
+        <v>153</v>
+      </c>
+      <c r="C34" s="38">
+        <v>46272</v>
+      </c>
+      <c r="D34" s="37">
+        <v>3026789043</v>
+      </c>
+      <c r="E34" s="37" t="s">
+        <v>70</v>
+      </c>
+      <c r="F34" s="39" t="s">
+        <v>56</v>
+      </c>
+      <c r="G34" s="37" t="s">
+        <v>63</v>
+      </c>
+      <c r="H34" s="37" t="s">
+        <v>177</v>
+      </c>
+      <c r="I34" s="37" t="s">
+        <v>217</v>
+      </c>
+      <c r="J34" s="37" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A35" s="37" t="s">
+        <v>35</v>
+      </c>
+      <c r="B35" s="37" t="s">
+        <v>153</v>
+      </c>
+      <c r="C35" s="38">
+        <v>46272</v>
+      </c>
+      <c r="D35" s="37">
+        <v>3026789043</v>
+      </c>
+      <c r="E35" s="37" t="s">
+        <v>70</v>
+      </c>
+      <c r="F35" s="39" t="s">
+        <v>56</v>
+      </c>
+      <c r="G35" s="37" t="s">
+        <v>63</v>
+      </c>
+      <c r="H35" s="37" t="s">
+        <v>164</v>
+      </c>
+      <c r="I35" s="37" t="s">
+        <v>216</v>
+      </c>
+      <c r="J35" s="37" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A36" s="40" t="s">
         <v>36</v>
       </c>
-      <c r="B23" s="6" t="s">
+      <c r="B36" s="40" t="s">
         <v>148</v>
       </c>
-      <c r="C23" s="7">
-        <v>46272</v>
-      </c>
-      <c r="D23" s="6">
+      <c r="C36" s="41">
+        <v>46272</v>
+      </c>
+      <c r="D36" s="40">
         <v>3037890154</v>
       </c>
-      <c r="E23" s="6" t="s">
+      <c r="E36" s="40" t="s">
         <v>69</v>
       </c>
-      <c r="F23" s="9" t="s">
+      <c r="F36" s="42" t="s">
         <v>57</v>
       </c>
-      <c r="G23" s="6" t="s">
+      <c r="G36" s="40" t="s">
         <v>37</v>
       </c>
-      <c r="H23" s="6" t="s">
-        <v>99</v>
-      </c>
-      <c r="I23" s="6" t="s">
-        <v>130</v>
-      </c>
-      <c r="J23" s="6" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="24" spans="1:10" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="6" t="s">
+      <c r="H36" s="40" t="s">
+        <v>164</v>
+      </c>
+      <c r="I36" s="40" t="s">
+        <v>219</v>
+      </c>
+      <c r="J36" s="40" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A37" s="40" t="s">
+        <v>36</v>
+      </c>
+      <c r="B37" s="40" t="s">
+        <v>148</v>
+      </c>
+      <c r="C37" s="41">
+        <v>46272</v>
+      </c>
+      <c r="D37" s="40">
+        <v>3037890154</v>
+      </c>
+      <c r="E37" s="40" t="s">
+        <v>69</v>
+      </c>
+      <c r="F37" s="42" t="s">
+        <v>57</v>
+      </c>
+      <c r="G37" s="40" t="s">
+        <v>37</v>
+      </c>
+      <c r="H37" s="40" t="s">
+        <v>158</v>
+      </c>
+      <c r="I37" s="40" t="s">
+        <v>159</v>
+      </c>
+      <c r="J37" s="40" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A38" s="19" t="s">
         <v>38</v>
       </c>
-      <c r="B24" s="6" t="s">
+      <c r="B38" s="19" t="s">
         <v>39</v>
       </c>
-      <c r="C24" s="7">
-        <v>46272</v>
-      </c>
-      <c r="D24" s="6">
+      <c r="C38" s="20">
+        <v>46272</v>
+      </c>
+      <c r="D38" s="19">
         <v>3048901265</v>
       </c>
-      <c r="E24" s="6" t="s">
+      <c r="E38" s="19" t="s">
         <v>68</v>
       </c>
-      <c r="F24" s="9" t="s">
+      <c r="F38" s="43" t="s">
         <v>58</v>
       </c>
-      <c r="G24" s="6" t="s">
+      <c r="G38" s="19" t="s">
         <v>40</v>
       </c>
-      <c r="H24" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="I24" s="6" t="s">
-        <v>132</v>
-      </c>
-      <c r="J24" s="6" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="6" t="s">
+      <c r="H38" s="19" t="s">
+        <v>165</v>
+      </c>
+      <c r="I38" s="19" t="s">
+        <v>221</v>
+      </c>
+      <c r="J38" s="19" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="19" t="s">
+        <v>38</v>
+      </c>
+      <c r="B39" s="19" t="s">
+        <v>39</v>
+      </c>
+      <c r="C39" s="20">
+        <v>46272</v>
+      </c>
+      <c r="D39" s="19">
+        <v>3048901265</v>
+      </c>
+      <c r="E39" s="19" t="s">
+        <v>68</v>
+      </c>
+      <c r="F39" s="43" t="s">
+        <v>58</v>
+      </c>
+      <c r="G39" s="19" t="s">
+        <v>40</v>
+      </c>
+      <c r="H39" s="19" t="s">
+        <v>170</v>
+      </c>
+      <c r="I39" s="19" t="s">
+        <v>189</v>
+      </c>
+      <c r="J39" s="19" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A40" s="19" t="s">
+        <v>38</v>
+      </c>
+      <c r="B40" s="19" t="s">
+        <v>39</v>
+      </c>
+      <c r="C40" s="20">
+        <v>46272</v>
+      </c>
+      <c r="D40" s="19">
+        <v>3048901265</v>
+      </c>
+      <c r="E40" s="19" t="s">
+        <v>68</v>
+      </c>
+      <c r="F40" s="43" t="s">
+        <v>58</v>
+      </c>
+      <c r="G40" s="19" t="s">
+        <v>40</v>
+      </c>
+      <c r="H40" s="19" t="s">
+        <v>171</v>
+      </c>
+      <c r="I40" s="19" t="s">
+        <v>179</v>
+      </c>
+      <c r="J40" s="19" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A41" s="44" t="s">
         <v>41</v>
       </c>
-      <c r="B25" s="6" t="s">
+      <c r="B41" s="44" t="s">
         <v>149</v>
       </c>
-      <c r="C25" s="7">
-        <v>46272</v>
-      </c>
-      <c r="D25" s="6">
+      <c r="C41" s="45">
+        <v>46272</v>
+      </c>
+      <c r="D41" s="44">
         <v>3059012376</v>
       </c>
-      <c r="E25" s="6" t="s">
+      <c r="E41" s="44" t="s">
         <v>82</v>
       </c>
-      <c r="F25" s="9" t="s">
+      <c r="F41" s="46" t="s">
         <v>59</v>
       </c>
-      <c r="G25" s="6" t="s">
+      <c r="G41" s="44" t="s">
         <v>63</v>
       </c>
-      <c r="H25" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="I25" s="6" t="s">
-        <v>134</v>
-      </c>
-      <c r="J25" s="6" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="26" spans="1:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="6" t="s">
+      <c r="H41" s="44" t="s">
+        <v>171</v>
+      </c>
+      <c r="I41" s="44" t="s">
+        <v>223</v>
+      </c>
+      <c r="J41" s="44" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A42" s="44" t="s">
+        <v>41</v>
+      </c>
+      <c r="B42" s="44" t="s">
+        <v>149</v>
+      </c>
+      <c r="C42" s="45">
+        <v>46272</v>
+      </c>
+      <c r="D42" s="44">
+        <v>3059012376</v>
+      </c>
+      <c r="E42" s="44" t="s">
+        <v>82</v>
+      </c>
+      <c r="F42" s="46" t="s">
+        <v>59</v>
+      </c>
+      <c r="G42" s="44" t="s">
+        <v>63</v>
+      </c>
+      <c r="H42" s="44" t="s">
+        <v>157</v>
+      </c>
+      <c r="I42" s="44" t="s">
+        <v>199</v>
+      </c>
+      <c r="J42" s="44" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A43" s="47" t="s">
         <v>42</v>
       </c>
-      <c r="B26" s="6" t="s">
+      <c r="B43" s="47" t="s">
         <v>150</v>
       </c>
-      <c r="C26" s="7">
-        <v>46272</v>
-      </c>
-      <c r="D26" s="6">
+      <c r="C43" s="48">
+        <v>46272</v>
+      </c>
+      <c r="D43" s="47">
         <v>3060123487</v>
       </c>
-      <c r="E26" s="6" t="s">
+      <c r="E43" s="47" t="s">
         <v>83</v>
       </c>
-      <c r="F26" s="9" t="s">
+      <c r="F43" s="49" t="s">
         <v>60</v>
       </c>
-      <c r="G26" s="6" t="s">
+      <c r="G43" s="47" t="s">
         <v>28</v>
       </c>
-      <c r="H26" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="I26" s="6" t="s">
-        <v>136</v>
-      </c>
-      <c r="J26" s="6" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="27" spans="1:10" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="6" t="s">
+      <c r="H43" s="47" t="s">
+        <v>164</v>
+      </c>
+      <c r="I43" s="47" t="s">
+        <v>216</v>
+      </c>
+      <c r="J43" s="47" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A44" s="47" t="s">
+        <v>42</v>
+      </c>
+      <c r="B44" s="47" t="s">
+        <v>150</v>
+      </c>
+      <c r="C44" s="48">
+        <v>46272</v>
+      </c>
+      <c r="D44" s="47">
+        <v>3060123487</v>
+      </c>
+      <c r="E44" s="47" t="s">
+        <v>83</v>
+      </c>
+      <c r="F44" s="49" t="s">
+        <v>60</v>
+      </c>
+      <c r="G44" s="47" t="s">
+        <v>28</v>
+      </c>
+      <c r="H44" s="47" t="s">
+        <v>165</v>
+      </c>
+      <c r="I44" s="47" t="s">
+        <v>200</v>
+      </c>
+      <c r="J44" s="47" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A45" s="47" t="s">
+        <v>42</v>
+      </c>
+      <c r="B45" s="47" t="s">
+        <v>150</v>
+      </c>
+      <c r="C45" s="48">
+        <v>46272</v>
+      </c>
+      <c r="D45" s="47">
+        <v>3060123487</v>
+      </c>
+      <c r="E45" s="47" t="s">
+        <v>83</v>
+      </c>
+      <c r="F45" s="49" t="s">
+        <v>60</v>
+      </c>
+      <c r="G45" s="47" t="s">
+        <v>28</v>
+      </c>
+      <c r="H45" s="47" t="s">
+        <v>158</v>
+      </c>
+      <c r="I45" s="47" t="s">
+        <v>198</v>
+      </c>
+      <c r="J45" s="47" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A46" s="50" t="s">
         <v>43</v>
       </c>
-      <c r="B27" s="6" t="s">
+      <c r="B46" s="50" t="s">
         <v>151</v>
       </c>
-      <c r="C27" s="7">
-        <v>46272</v>
-      </c>
-      <c r="D27" s="6">
+      <c r="C46" s="51">
+        <v>46272</v>
+      </c>
+      <c r="D46" s="50">
         <v>3071234598</v>
       </c>
-      <c r="E27" s="6" t="s">
+      <c r="E46" s="50" t="s">
         <v>84</v>
       </c>
-      <c r="F27" s="9" t="s">
+      <c r="F46" s="52" t="s">
         <v>61</v>
       </c>
-      <c r="G27" s="6" t="s">
+      <c r="G46" s="50" t="s">
         <v>44</v>
       </c>
-      <c r="H27" s="6" t="s">
-        <v>91</v>
-      </c>
-      <c r="I27" s="6" t="s">
-        <v>138</v>
-      </c>
-      <c r="J27" s="6" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="28" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="6" t="s">
+      <c r="H46" s="50" t="s">
+        <v>157</v>
+      </c>
+      <c r="I46" s="50" t="s">
+        <v>204</v>
+      </c>
+      <c r="J46" s="50" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A47" s="50" t="s">
+        <v>43</v>
+      </c>
+      <c r="B47" s="50" t="s">
+        <v>151</v>
+      </c>
+      <c r="C47" s="51">
+        <v>46272</v>
+      </c>
+      <c r="D47" s="50">
+        <v>3071234598</v>
+      </c>
+      <c r="E47" s="50" t="s">
+        <v>84</v>
+      </c>
+      <c r="F47" s="52" t="s">
+        <v>61</v>
+      </c>
+      <c r="G47" s="50" t="s">
+        <v>44</v>
+      </c>
+      <c r="H47" s="50" t="s">
+        <v>170</v>
+      </c>
+      <c r="I47" s="50" t="s">
+        <v>189</v>
+      </c>
+      <c r="J47" s="50" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A48" s="16" t="s">
         <v>45</v>
       </c>
-      <c r="B28" s="6" t="s">
+      <c r="B48" s="16" t="s">
         <v>46</v>
       </c>
-      <c r="C28" s="7">
-        <v>46272</v>
-      </c>
-      <c r="D28" s="6">
+      <c r="C48" s="17">
+        <v>46272</v>
+      </c>
+      <c r="D48" s="16">
         <v>3082345609</v>
       </c>
-      <c r="E28" s="6" t="s">
+      <c r="E48" s="16" t="s">
         <v>85</v>
       </c>
-      <c r="F28" s="9" t="s">
+      <c r="F48" s="18" t="s">
         <v>62</v>
       </c>
-      <c r="G28" s="6" t="s">
+      <c r="G48" s="16" t="s">
         <v>63</v>
       </c>
-      <c r="H28" s="6" t="s">
-        <v>103</v>
-      </c>
-      <c r="I28" s="6" t="s">
-        <v>140</v>
-      </c>
-      <c r="J28" s="6" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A32" s="1"/>
-      <c r="B32" s="1"/>
-      <c r="C32" s="1"/>
-      <c r="D32" s="1"/>
-      <c r="E32" s="1"/>
-      <c r="F32" s="1"/>
-      <c r="G32" s="1"/>
-    </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A33" s="2"/>
-      <c r="B33" s="2"/>
-      <c r="C33" s="3"/>
-      <c r="D33" s="2"/>
-      <c r="E33" s="2"/>
-      <c r="F33" s="4"/>
-      <c r="G33" s="2"/>
-    </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A34" s="2"/>
-      <c r="B34" s="2"/>
-      <c r="C34" s="3"/>
-      <c r="D34" s="2"/>
-      <c r="E34" s="2"/>
-      <c r="F34" s="4"/>
-      <c r="G34" s="2"/>
-    </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A35" s="2"/>
-      <c r="B35" s="2"/>
-      <c r="C35" s="3"/>
-      <c r="D35" s="2"/>
-      <c r="E35" s="2"/>
-      <c r="F35" s="4"/>
-      <c r="G35" s="2"/>
-    </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A36" s="2"/>
-      <c r="B36" s="2"/>
-      <c r="C36" s="3"/>
-      <c r="D36" s="2"/>
-      <c r="E36" s="2"/>
-      <c r="F36" s="4"/>
-      <c r="G36" s="2"/>
-    </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A37" s="2"/>
-      <c r="B37" s="2"/>
-      <c r="C37" s="3"/>
-      <c r="D37" s="2"/>
-      <c r="E37" s="2"/>
-      <c r="F37" s="4"/>
-      <c r="G37" s="2"/>
-    </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A38" s="2"/>
-      <c r="B38" s="2"/>
-      <c r="C38" s="3"/>
-      <c r="D38" s="2"/>
-      <c r="E38" s="2"/>
-      <c r="F38" s="4"/>
-      <c r="G38" s="2"/>
-    </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A39" s="2"/>
-      <c r="B39" s="2"/>
-      <c r="C39" s="3"/>
-      <c r="D39" s="2"/>
-      <c r="E39" s="2"/>
-      <c r="F39" s="4"/>
-      <c r="G39" s="2"/>
-    </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A40" s="2"/>
-      <c r="B40" s="2"/>
-      <c r="C40" s="3"/>
-      <c r="D40" s="2"/>
-      <c r="E40" s="2"/>
-      <c r="F40" s="4"/>
-      <c r="G40" s="2"/>
-    </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A41" s="2"/>
-      <c r="B41" s="2"/>
-      <c r="C41" s="3"/>
-      <c r="D41" s="2"/>
-      <c r="E41" s="2"/>
-      <c r="F41" s="4"/>
-      <c r="G41" s="2"/>
-    </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A42" s="2"/>
-      <c r="B42" s="2"/>
-      <c r="C42" s="3"/>
-      <c r="D42" s="2"/>
-      <c r="E42" s="2"/>
-      <c r="F42" s="4"/>
-      <c r="G42" s="2"/>
-    </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A43" s="2"/>
-      <c r="B43" s="2"/>
-      <c r="C43" s="3"/>
-      <c r="D43" s="2"/>
-      <c r="E43" s="2"/>
-      <c r="F43" s="4"/>
-      <c r="G43" s="2"/>
-    </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A44" s="2"/>
-      <c r="B44" s="2"/>
-      <c r="C44" s="3"/>
-      <c r="D44" s="2"/>
-      <c r="E44" s="2"/>
-      <c r="F44" s="4"/>
-      <c r="G44" s="2"/>
-    </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A45" s="2"/>
-      <c r="B45" s="2"/>
-      <c r="C45" s="3"/>
-      <c r="D45" s="2"/>
-      <c r="E45" s="2"/>
-      <c r="F45" s="4"/>
-      <c r="G45" s="2"/>
-    </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A46" s="2"/>
-      <c r="B46" s="2"/>
-      <c r="C46" s="3"/>
-      <c r="D46" s="2"/>
-      <c r="E46" s="2"/>
-      <c r="F46" s="4"/>
-      <c r="G46" s="2"/>
-    </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A47" s="2"/>
-      <c r="B47" s="2"/>
-      <c r="C47" s="3"/>
-      <c r="D47" s="2"/>
-      <c r="E47" s="2"/>
-      <c r="F47" s="4"/>
-      <c r="G47" s="2"/>
-    </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A48" s="2"/>
-      <c r="B48" s="2"/>
-      <c r="C48" s="3"/>
-      <c r="D48" s="2"/>
-      <c r="E48" s="2"/>
-      <c r="F48" s="4"/>
-      <c r="G48" s="2"/>
-    </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A49" s="2"/>
-      <c r="B49" s="2"/>
-      <c r="C49" s="3"/>
-      <c r="D49" s="2"/>
-      <c r="E49" s="2"/>
-      <c r="F49" s="4"/>
-      <c r="G49" s="2"/>
-    </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A50" s="2"/>
-      <c r="B50" s="2"/>
-      <c r="C50" s="3"/>
-      <c r="D50" s="2"/>
-      <c r="E50" s="2"/>
-      <c r="F50" s="4"/>
-      <c r="G50" s="2"/>
-    </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A51" s="2"/>
-      <c r="B51" s="2"/>
-      <c r="C51" s="3"/>
-      <c r="D51" s="2"/>
-      <c r="E51" s="2"/>
-      <c r="F51" s="4"/>
-      <c r="G51" s="2"/>
+      <c r="H48" s="16" t="s">
+        <v>170</v>
+      </c>
+      <c r="I48" s="16" t="s">
+        <v>208</v>
+      </c>
+      <c r="J48" s="16" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A49" s="16" t="s">
+        <v>45</v>
+      </c>
+      <c r="B49" s="16" t="s">
+        <v>46</v>
+      </c>
+      <c r="C49" s="17">
+        <v>46272</v>
+      </c>
+      <c r="D49" s="16">
+        <v>3082345609</v>
+      </c>
+      <c r="E49" s="16" t="s">
+        <v>85</v>
+      </c>
+      <c r="F49" s="18" t="s">
+        <v>62</v>
+      </c>
+      <c r="G49" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="H49" s="16" t="s">
+        <v>171</v>
+      </c>
+      <c r="I49" s="16" t="s">
+        <v>161</v>
+      </c>
+      <c r="J49" s="16" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="50" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A50" s="16" t="s">
+        <v>45</v>
+      </c>
+      <c r="B50" s="16" t="s">
+        <v>46</v>
+      </c>
+      <c r="C50" s="17">
+        <v>46272</v>
+      </c>
+      <c r="D50" s="16">
+        <v>3082345609</v>
+      </c>
+      <c r="E50" s="16" t="s">
+        <v>85</v>
+      </c>
+      <c r="F50" s="18" t="s">
+        <v>62</v>
+      </c>
+      <c r="G50" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="H50" s="16" t="s">
+        <v>177</v>
+      </c>
+      <c r="I50" s="16" t="s">
+        <v>209</v>
+      </c>
+      <c r="J50" s="16" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="54" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A54" s="1"/>
+      <c r="B54" s="1"/>
+      <c r="C54" s="1"/>
+      <c r="D54" s="1"/>
+      <c r="E54" s="1"/>
+      <c r="F54" s="1"/>
+      <c r="G54" s="1"/>
+    </row>
+    <row r="55" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A55" s="2"/>
+      <c r="B55" s="2"/>
+      <c r="C55" s="3"/>
+      <c r="D55" s="2"/>
+      <c r="E55" s="2"/>
+      <c r="F55" s="4"/>
+      <c r="G55" s="2"/>
+    </row>
+    <row r="56" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A56" s="2"/>
+      <c r="B56" s="2"/>
+      <c r="C56" s="3"/>
+      <c r="D56" s="2"/>
+      <c r="E56" s="2"/>
+      <c r="F56" s="4"/>
+      <c r="G56" s="2"/>
+    </row>
+    <row r="57" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A57" s="2"/>
+      <c r="B57" s="2"/>
+      <c r="C57" s="3"/>
+      <c r="D57" s="2"/>
+      <c r="E57" s="2"/>
+      <c r="F57" s="4"/>
+      <c r="G57" s="2"/>
+    </row>
+    <row r="58" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A58" s="2"/>
+      <c r="B58" s="2"/>
+      <c r="C58" s="3"/>
+      <c r="D58" s="2"/>
+      <c r="E58" s="2"/>
+      <c r="F58" s="4"/>
+      <c r="G58" s="2"/>
+    </row>
+    <row r="59" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A59" s="2"/>
+      <c r="B59" s="2"/>
+      <c r="C59" s="3"/>
+      <c r="D59" s="2"/>
+      <c r="E59" s="2"/>
+      <c r="F59" s="4"/>
+      <c r="G59" s="2"/>
+    </row>
+    <row r="60" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A60" s="2"/>
+      <c r="B60" s="2"/>
+      <c r="C60" s="3"/>
+      <c r="D60" s="2"/>
+      <c r="E60" s="2"/>
+      <c r="F60" s="4"/>
+      <c r="G60" s="2"/>
+    </row>
+    <row r="61" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A61" s="2"/>
+      <c r="B61" s="2"/>
+      <c r="C61" s="3"/>
+      <c r="D61" s="2"/>
+      <c r="E61" s="2"/>
+      <c r="F61" s="4"/>
+      <c r="G61" s="2"/>
+    </row>
+    <row r="62" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A62" s="2"/>
+      <c r="B62" s="2"/>
+      <c r="C62" s="3"/>
+      <c r="D62" s="2"/>
+      <c r="E62" s="2"/>
+      <c r="F62" s="4"/>
+      <c r="G62" s="2"/>
+    </row>
+    <row r="63" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A63" s="2"/>
+      <c r="B63" s="2"/>
+      <c r="C63" s="3"/>
+      <c r="D63" s="2"/>
+      <c r="E63" s="2"/>
+      <c r="F63" s="4"/>
+      <c r="G63" s="2"/>
+    </row>
+    <row r="64" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A64" s="2"/>
+      <c r="B64" s="2"/>
+      <c r="C64" s="3"/>
+      <c r="D64" s="2"/>
+      <c r="E64" s="2"/>
+      <c r="F64" s="4"/>
+      <c r="G64" s="2"/>
+    </row>
+    <row r="65" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A65" s="2"/>
+      <c r="B65" s="2"/>
+      <c r="C65" s="3"/>
+      <c r="D65" s="2"/>
+      <c r="E65" s="2"/>
+      <c r="F65" s="4"/>
+      <c r="G65" s="2"/>
+    </row>
+    <row r="66" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A66" s="2"/>
+      <c r="B66" s="2"/>
+      <c r="C66" s="3"/>
+      <c r="D66" s="2"/>
+      <c r="E66" s="2"/>
+      <c r="F66" s="4"/>
+      <c r="G66" s="2"/>
+    </row>
+    <row r="67" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A67" s="2"/>
+      <c r="B67" s="2"/>
+      <c r="C67" s="3"/>
+      <c r="D67" s="2"/>
+      <c r="E67" s="2"/>
+      <c r="F67" s="4"/>
+      <c r="G67" s="2"/>
+    </row>
+    <row r="68" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A68" s="2"/>
+      <c r="B68" s="2"/>
+      <c r="C68" s="3"/>
+      <c r="D68" s="2"/>
+      <c r="E68" s="2"/>
+      <c r="F68" s="4"/>
+      <c r="G68" s="2"/>
+    </row>
+    <row r="69" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A69" s="2"/>
+      <c r="B69" s="2"/>
+      <c r="C69" s="3"/>
+      <c r="D69" s="2"/>
+      <c r="E69" s="2"/>
+      <c r="F69" s="4"/>
+      <c r="G69" s="2"/>
+    </row>
+    <row r="70" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A70" s="2"/>
+      <c r="B70" s="2"/>
+      <c r="C70" s="3"/>
+      <c r="D70" s="2"/>
+      <c r="E70" s="2"/>
+      <c r="F70" s="4"/>
+      <c r="G70" s="2"/>
+    </row>
+    <row r="71" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A71" s="2"/>
+      <c r="B71" s="2"/>
+      <c r="C71" s="3"/>
+      <c r="D71" s="2"/>
+      <c r="E71" s="2"/>
+      <c r="F71" s="4"/>
+      <c r="G71" s="2"/>
+    </row>
+    <row r="72" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A72" s="2"/>
+      <c r="B72" s="2"/>
+      <c r="C72" s="3"/>
+      <c r="D72" s="2"/>
+      <c r="E72" s="2"/>
+      <c r="F72" s="4"/>
+      <c r="G72" s="2"/>
+    </row>
+    <row r="73" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A73" s="2"/>
+      <c r="B73" s="2"/>
+      <c r="C73" s="3"/>
+      <c r="D73" s="2"/>
+      <c r="E73" s="2"/>
+      <c r="F73" s="4"/>
+      <c r="G73" s="2"/>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="F6" r:id="rId1" xr:uid="{6326BC65-0AC6-40CF-A76D-14B409E0134B}"/>
     <hyperlink ref="F9" r:id="rId2" xr:uid="{D88A0B46-DBA1-4568-ABBB-E1A890937830}"/>
-    <hyperlink ref="F17" r:id="rId3" xr:uid="{A51E2D82-DF9B-46D7-B79B-E43BC71EADBE}"/>
-    <hyperlink ref="F18" r:id="rId4" xr:uid="{E072F17F-AF51-4AE5-8A7F-A13CA911E563}"/>
-    <hyperlink ref="F19" r:id="rId5" xr:uid="{58EA014F-D83F-48BF-BADE-67BCA9BEF585}"/>
-    <hyperlink ref="F16" r:id="rId6" xr:uid="{8AD8FC03-429B-4FD7-BDF7-82BE8D4E6337}"/>
-    <hyperlink ref="F20" r:id="rId7" xr:uid="{75B1B474-E684-4161-B983-6A2F6CCA185A}"/>
-    <hyperlink ref="F21" r:id="rId8" xr:uid="{40E30AD9-BEDA-4A27-8BDE-158EC7180ECE}"/>
-    <hyperlink ref="F22" r:id="rId9" xr:uid="{BE08C16A-4E93-406A-BA0B-35B62ABEC2AA}"/>
-    <hyperlink ref="F23" r:id="rId10" xr:uid="{E2524138-4615-462E-8D0A-04B1773291D0}"/>
-    <hyperlink ref="F24" r:id="rId11" xr:uid="{08F09F79-8731-44B5-93EF-9E082C4F2254}"/>
-    <hyperlink ref="F25" r:id="rId12" xr:uid="{D272E36F-85B9-4196-8BF0-8D3EF050FABB}"/>
-    <hyperlink ref="F26" r:id="rId13" xr:uid="{E509F268-7FCA-43E2-9480-12E9C0B1E001}"/>
-    <hyperlink ref="F27" r:id="rId14" xr:uid="{650D3E9E-C3B8-4380-B4E6-05224EB62ECD}"/>
-    <hyperlink ref="F28" r:id="rId15" xr:uid="{95EAB623-BDE2-4053-8CF4-C4F073C0B5CD}"/>
+    <hyperlink ref="F20" r:id="rId3" xr:uid="{A51E2D82-DF9B-46D7-B79B-E43BC71EADBE}"/>
+    <hyperlink ref="F22" r:id="rId4" xr:uid="{E072F17F-AF51-4AE5-8A7F-A13CA911E563}"/>
+    <hyperlink ref="F25" r:id="rId5" xr:uid="{58EA014F-D83F-48BF-BADE-67BCA9BEF585}"/>
+    <hyperlink ref="F17" r:id="rId6" xr:uid="{8AD8FC03-429B-4FD7-BDF7-82BE8D4E6337}"/>
+    <hyperlink ref="F28" r:id="rId7" xr:uid="{75B1B474-E684-4161-B983-6A2F6CCA185A}"/>
+    <hyperlink ref="F30" r:id="rId8" xr:uid="{40E30AD9-BEDA-4A27-8BDE-158EC7180ECE}"/>
+    <hyperlink ref="F33" r:id="rId9" xr:uid="{BE08C16A-4E93-406A-BA0B-35B62ABEC2AA}"/>
+    <hyperlink ref="F36" r:id="rId10" xr:uid="{E2524138-4615-462E-8D0A-04B1773291D0}"/>
+    <hyperlink ref="F38" r:id="rId11" xr:uid="{08F09F79-8731-44B5-93EF-9E082C4F2254}"/>
+    <hyperlink ref="F41" r:id="rId12" xr:uid="{D272E36F-85B9-4196-8BF0-8D3EF050FABB}"/>
+    <hyperlink ref="F43" r:id="rId13" xr:uid="{E509F268-7FCA-43E2-9480-12E9C0B1E001}"/>
+    <hyperlink ref="F46" r:id="rId14" xr:uid="{650D3E9E-C3B8-4380-B4E6-05224EB62ECD}"/>
+    <hyperlink ref="F50" r:id="rId15" xr:uid="{95EAB623-BDE2-4053-8CF4-C4F073C0B5CD}"/>
     <hyperlink ref="F15" r:id="rId16" xr:uid="{D5703FBC-EB8E-4E88-A312-6AE225A408E7}"/>
     <hyperlink ref="F12" r:id="rId17" xr:uid="{A62E5892-D8AA-4021-95C3-56FD52B8C8F9}"/>
     <hyperlink ref="F11" r:id="rId18" xr:uid="{14893CA0-E2B4-4AA4-997B-4120BDEE235B}"/>
@@ -3005,8 +3954,1881 @@
     <hyperlink ref="F10" r:id="rId22" xr:uid="{5CA48F6C-8D9E-47C3-AB82-E1B408B4F7C4}"/>
     <hyperlink ref="F13" r:id="rId23" xr:uid="{7641A20B-8D54-402B-B9B9-A87B8C48DCFA}"/>
     <hyperlink ref="F14" r:id="rId24" xr:uid="{60C28499-7AC6-493A-A69E-96EE88713BA4}"/>
+    <hyperlink ref="F16" r:id="rId25" xr:uid="{8FB21F49-C847-4EBA-A534-FDBD063F0D9E}"/>
+    <hyperlink ref="F18" r:id="rId26" xr:uid="{A0284FE4-120C-46EB-8FB0-9A6247E7D10B}"/>
+    <hyperlink ref="F19" r:id="rId27" xr:uid="{B2DBA27A-FCBC-4677-9339-5DD3198830D7}"/>
+    <hyperlink ref="F21" r:id="rId28" xr:uid="{32A89053-2809-4690-803B-B2EFC3A97F7E}"/>
+    <hyperlink ref="F23" r:id="rId29" xr:uid="{70B1C3D6-560F-41E4-A316-B92C4B5BCED3}"/>
+    <hyperlink ref="F24" r:id="rId30" xr:uid="{EDF559F4-FFCA-49B8-B4DB-8B9D432FAFD7}"/>
+    <hyperlink ref="F26" r:id="rId31" xr:uid="{8A127BBC-A957-4024-9616-22D3C7765BDB}"/>
+    <hyperlink ref="F27" r:id="rId32" xr:uid="{6784EA08-C03F-46E2-948C-E99D019AAA93}"/>
+    <hyperlink ref="F29" r:id="rId33" xr:uid="{3833D74E-E298-4F56-AB0B-C2B5F0B67789}"/>
+    <hyperlink ref="F31" r:id="rId34" xr:uid="{BB5677F0-A0E5-4223-A991-B8A6171FDD2C}"/>
+    <hyperlink ref="F32" r:id="rId35" xr:uid="{6E82C058-6666-47D4-B6C6-0662E338D13A}"/>
+    <hyperlink ref="F34" r:id="rId36" xr:uid="{A7B0ABC4-4B89-4B73-A083-F7368CB11F52}"/>
+    <hyperlink ref="F35" r:id="rId37" xr:uid="{DAEBCF1D-D75B-4925-BE79-57F20C780BB7}"/>
+    <hyperlink ref="F37" r:id="rId38" xr:uid="{7740942D-69A1-4008-AF8F-7C18DDE3A5BA}"/>
+    <hyperlink ref="F39" r:id="rId39" xr:uid="{FB5B3A5E-398E-484C-B769-D62F9A04CDBB}"/>
+    <hyperlink ref="F40" r:id="rId40" xr:uid="{BA66EC4A-B96C-4D05-B135-789722155E7A}"/>
+    <hyperlink ref="F42" r:id="rId41" xr:uid="{653AE5B9-6098-4DE5-BB17-05722F56510B}"/>
+    <hyperlink ref="F44" r:id="rId42" xr:uid="{4D3F77C5-C5E3-46BA-8171-367C230B3DFA}"/>
+    <hyperlink ref="F45" r:id="rId43" xr:uid="{081E26DC-1780-4E7C-83C7-A2E3E9D703D2}"/>
+    <hyperlink ref="F48" r:id="rId44" xr:uid="{93F27390-220F-4A38-8A2D-EE1E44139741}"/>
+    <hyperlink ref="F49" r:id="rId45" xr:uid="{EEDFA7D2-9BD7-46F0-93CB-2054F0B81681}"/>
+    <hyperlink ref="F47" r:id="rId46" xr:uid="{B2F214BC-3C58-43D9-82C6-3460CF1C973E}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId25"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId47"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{112793D1-BC6A-4449-A31D-CCC44D309781}">
+  <dimension ref="A1:J73"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="28.7109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="29" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="20" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="22.28515625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="I1" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="J1" s="5" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2" s="19" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2" s="19" t="s">
+        <v>146</v>
+      </c>
+      <c r="C2" s="20">
+        <v>46272</v>
+      </c>
+      <c r="D2" s="19">
+        <v>3104567821</v>
+      </c>
+      <c r="E2" s="19" t="s">
+        <v>67</v>
+      </c>
+      <c r="F2" s="21" t="s">
+        <v>47</v>
+      </c>
+      <c r="G2" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="H2" s="19" t="s">
+        <v>171</v>
+      </c>
+      <c r="I2" s="19" t="s">
+        <v>161</v>
+      </c>
+      <c r="J2" s="19" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A3" s="19" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" s="19" t="s">
+        <v>146</v>
+      </c>
+      <c r="C3" s="20">
+        <v>46272</v>
+      </c>
+      <c r="D3" s="19">
+        <v>3104567821</v>
+      </c>
+      <c r="E3" s="19" t="s">
+        <v>67</v>
+      </c>
+      <c r="F3" s="21" t="s">
+        <v>47</v>
+      </c>
+      <c r="G3" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="H3" s="19" t="s">
+        <v>157</v>
+      </c>
+      <c r="I3" s="19" t="s">
+        <v>160</v>
+      </c>
+      <c r="J3" s="19" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A4" s="19" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" s="19" t="s">
+        <v>146</v>
+      </c>
+      <c r="C4" s="20">
+        <v>46272</v>
+      </c>
+      <c r="D4" s="19">
+        <v>3104567821</v>
+      </c>
+      <c r="E4" s="19" t="s">
+        <v>67</v>
+      </c>
+      <c r="F4" s="21" t="s">
+        <v>47</v>
+      </c>
+      <c r="G4" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="H4" s="19" t="s">
+        <v>158</v>
+      </c>
+      <c r="I4" s="19" t="s">
+        <v>159</v>
+      </c>
+      <c r="J4" s="19" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A5" s="16" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="C5" s="17">
+        <v>46272</v>
+      </c>
+      <c r="D5" s="16">
+        <v>3115678932</v>
+      </c>
+      <c r="E5" s="16" t="s">
+        <v>80</v>
+      </c>
+      <c r="F5" s="18" t="s">
+        <v>48</v>
+      </c>
+      <c r="G5" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="H5" s="16" t="s">
+        <v>164</v>
+      </c>
+      <c r="I5" s="16" t="s">
+        <v>167</v>
+      </c>
+      <c r="J5" s="16" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A6" s="16" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="C6" s="17">
+        <v>46272</v>
+      </c>
+      <c r="D6" s="16">
+        <v>3115678932</v>
+      </c>
+      <c r="E6" s="16" t="s">
+        <v>80</v>
+      </c>
+      <c r="F6" s="18" t="s">
+        <v>48</v>
+      </c>
+      <c r="G6" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="H6" s="16" t="s">
+        <v>165</v>
+      </c>
+      <c r="I6" s="16" t="s">
+        <v>166</v>
+      </c>
+      <c r="J6" s="16" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A7" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="B7" s="13" t="s">
+        <v>145</v>
+      </c>
+      <c r="C7" s="14">
+        <v>46272</v>
+      </c>
+      <c r="D7" s="13">
+        <v>3126789043</v>
+      </c>
+      <c r="E7" s="13" t="s">
+        <v>81</v>
+      </c>
+      <c r="F7" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="G7" s="13" t="s">
+        <v>63</v>
+      </c>
+      <c r="H7" s="13" t="s">
+        <v>170</v>
+      </c>
+      <c r="I7" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="J7" s="13" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A8" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="B8" s="13" t="s">
+        <v>145</v>
+      </c>
+      <c r="C8" s="14">
+        <v>46272</v>
+      </c>
+      <c r="D8" s="13">
+        <v>3126789043</v>
+      </c>
+      <c r="E8" s="13" t="s">
+        <v>81</v>
+      </c>
+      <c r="F8" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="G8" s="13" t="s">
+        <v>63</v>
+      </c>
+      <c r="H8" s="13" t="s">
+        <v>171</v>
+      </c>
+      <c r="I8" s="13" t="s">
+        <v>173</v>
+      </c>
+      <c r="J8" s="13" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A9" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="B9" s="13" t="s">
+        <v>145</v>
+      </c>
+      <c r="C9" s="14">
+        <v>46272</v>
+      </c>
+      <c r="D9" s="13">
+        <v>3126789043</v>
+      </c>
+      <c r="E9" s="13" t="s">
+        <v>81</v>
+      </c>
+      <c r="F9" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="G9" s="13" t="s">
+        <v>63</v>
+      </c>
+      <c r="H9" s="13" t="s">
+        <v>157</v>
+      </c>
+      <c r="I9" s="13" t="s">
+        <v>172</v>
+      </c>
+      <c r="J9" s="13" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A10" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="B10" s="10" t="s">
+        <v>154</v>
+      </c>
+      <c r="C10" s="11">
+        <v>46272</v>
+      </c>
+      <c r="D10" s="10">
+        <v>3137890154</v>
+      </c>
+      <c r="E10" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="F10" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="G10" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="H10" s="10" t="s">
+        <v>171</v>
+      </c>
+      <c r="I10" s="10" t="s">
+        <v>179</v>
+      </c>
+      <c r="J10" s="10" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A11" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="B11" s="10" t="s">
+        <v>154</v>
+      </c>
+      <c r="C11" s="11">
+        <v>46272</v>
+      </c>
+      <c r="D11" s="10">
+        <v>3137890154</v>
+      </c>
+      <c r="E11" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="F11" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="G11" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="H11" s="10" t="s">
+        <v>177</v>
+      </c>
+      <c r="I11" s="10" t="s">
+        <v>178</v>
+      </c>
+      <c r="J11" s="10" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A12" s="22" t="s">
+        <v>18</v>
+      </c>
+      <c r="B12" s="22" t="s">
+        <v>155</v>
+      </c>
+      <c r="C12" s="23">
+        <v>46272</v>
+      </c>
+      <c r="D12" s="22">
+        <v>3148901265</v>
+      </c>
+      <c r="E12" s="22" t="s">
+        <v>78</v>
+      </c>
+      <c r="F12" s="24" t="s">
+        <v>65</v>
+      </c>
+      <c r="G12" s="22" t="s">
+        <v>19</v>
+      </c>
+      <c r="H12" s="22" t="s">
+        <v>158</v>
+      </c>
+      <c r="I12" s="22" t="s">
+        <v>159</v>
+      </c>
+      <c r="J12" s="22" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A13" s="22" t="s">
+        <v>18</v>
+      </c>
+      <c r="B13" s="22" t="s">
+        <v>155</v>
+      </c>
+      <c r="C13" s="23">
+        <v>46273</v>
+      </c>
+      <c r="D13" s="22">
+        <v>3148901266</v>
+      </c>
+      <c r="E13" s="22" t="s">
+        <v>77</v>
+      </c>
+      <c r="F13" s="24" t="s">
+        <v>65</v>
+      </c>
+      <c r="G13" s="22" t="s">
+        <v>19</v>
+      </c>
+      <c r="H13" s="22" t="s">
+        <v>183</v>
+      </c>
+      <c r="I13" s="22" t="s">
+        <v>184</v>
+      </c>
+      <c r="J13" s="22" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A14" s="22" t="s">
+        <v>18</v>
+      </c>
+      <c r="B14" s="22" t="s">
+        <v>155</v>
+      </c>
+      <c r="C14" s="23">
+        <v>46274</v>
+      </c>
+      <c r="D14" s="22">
+        <v>3148901267</v>
+      </c>
+      <c r="E14" s="22" t="s">
+        <v>182</v>
+      </c>
+      <c r="F14" s="24" t="s">
+        <v>65</v>
+      </c>
+      <c r="G14" s="22" t="s">
+        <v>19</v>
+      </c>
+      <c r="H14" s="22" t="s">
+        <v>165</v>
+      </c>
+      <c r="I14" s="22" t="s">
+        <v>185</v>
+      </c>
+      <c r="J14" s="22" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A15" s="25" t="s">
+        <v>20</v>
+      </c>
+      <c r="B15" s="25" t="s">
+        <v>152</v>
+      </c>
+      <c r="C15" s="26">
+        <v>46272</v>
+      </c>
+      <c r="D15" s="25">
+        <v>3159012376</v>
+      </c>
+      <c r="E15" s="25" t="s">
+        <v>77</v>
+      </c>
+      <c r="F15" s="27" t="s">
+        <v>64</v>
+      </c>
+      <c r="G15" s="25" t="s">
+        <v>63</v>
+      </c>
+      <c r="H15" s="25" t="s">
+        <v>157</v>
+      </c>
+      <c r="I15" s="25" t="s">
+        <v>190</v>
+      </c>
+      <c r="J15" s="25" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A16" s="25" t="s">
+        <v>20</v>
+      </c>
+      <c r="B16" s="25" t="s">
+        <v>152</v>
+      </c>
+      <c r="C16" s="26">
+        <v>46272</v>
+      </c>
+      <c r="D16" s="25">
+        <v>3159012376</v>
+      </c>
+      <c r="E16" s="25" t="s">
+        <v>77</v>
+      </c>
+      <c r="F16" s="27" t="s">
+        <v>64</v>
+      </c>
+      <c r="G16" s="25" t="s">
+        <v>63</v>
+      </c>
+      <c r="H16" s="25" t="s">
+        <v>170</v>
+      </c>
+      <c r="I16" s="25" t="s">
+        <v>189</v>
+      </c>
+      <c r="J16" s="25" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A17" s="28" t="s">
+        <v>21</v>
+      </c>
+      <c r="B17" s="28" t="s">
+        <v>142</v>
+      </c>
+      <c r="C17" s="29">
+        <v>46272</v>
+      </c>
+      <c r="D17" s="28">
+        <v>3160123487</v>
+      </c>
+      <c r="E17" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="F17" s="30" t="s">
+        <v>53</v>
+      </c>
+      <c r="G17" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="H17" s="28" t="s">
+        <v>171</v>
+      </c>
+      <c r="I17" s="28" t="s">
+        <v>197</v>
+      </c>
+      <c r="J17" s="28" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A18" s="28" t="s">
+        <v>21</v>
+      </c>
+      <c r="B18" s="28" t="s">
+        <v>142</v>
+      </c>
+      <c r="C18" s="29">
+        <v>46272</v>
+      </c>
+      <c r="D18" s="28">
+        <v>3160123487</v>
+      </c>
+      <c r="E18" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="F18" s="30" t="s">
+        <v>53</v>
+      </c>
+      <c r="G18" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="H18" s="28" t="s">
+        <v>196</v>
+      </c>
+      <c r="I18" s="28" t="s">
+        <v>198</v>
+      </c>
+      <c r="J18" s="28" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A19" s="28" t="s">
+        <v>21</v>
+      </c>
+      <c r="B19" s="28" t="s">
+        <v>142</v>
+      </c>
+      <c r="C19" s="29">
+        <v>46272</v>
+      </c>
+      <c r="D19" s="28">
+        <v>3160123487</v>
+      </c>
+      <c r="E19" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="F19" s="30" t="s">
+        <v>53</v>
+      </c>
+      <c r="G19" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="H19" s="28" t="s">
+        <v>157</v>
+      </c>
+      <c r="I19" s="28" t="s">
+        <v>199</v>
+      </c>
+      <c r="J19" s="28" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A20" s="31" t="s">
+        <v>23</v>
+      </c>
+      <c r="B20" s="31" t="s">
+        <v>24</v>
+      </c>
+      <c r="C20" s="32">
+        <v>46272</v>
+      </c>
+      <c r="D20" s="31">
+        <v>3171234598</v>
+      </c>
+      <c r="E20" s="31" t="s">
+        <v>75</v>
+      </c>
+      <c r="F20" s="33" t="s">
+        <v>50</v>
+      </c>
+      <c r="G20" s="31" t="s">
+        <v>25</v>
+      </c>
+      <c r="H20" s="31" t="s">
+        <v>165</v>
+      </c>
+      <c r="I20" s="31" t="s">
+        <v>200</v>
+      </c>
+      <c r="J20" s="31" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A21" s="31" t="s">
+        <v>23</v>
+      </c>
+      <c r="B21" s="31" t="s">
+        <v>24</v>
+      </c>
+      <c r="C21" s="32">
+        <v>46272</v>
+      </c>
+      <c r="D21" s="31">
+        <v>3171234598</v>
+      </c>
+      <c r="E21" s="31" t="s">
+        <v>75</v>
+      </c>
+      <c r="F21" s="33" t="s">
+        <v>50</v>
+      </c>
+      <c r="G21" s="31" t="s">
+        <v>25</v>
+      </c>
+      <c r="H21" s="31" t="s">
+        <v>183</v>
+      </c>
+      <c r="I21" s="31" t="s">
+        <v>167</v>
+      </c>
+      <c r="J21" s="31" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A22" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="B22" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="C22" s="14">
+        <v>46272</v>
+      </c>
+      <c r="D22" s="13">
+        <v>3182345609</v>
+      </c>
+      <c r="E22" s="13" t="s">
+        <v>74</v>
+      </c>
+      <c r="F22" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="G22" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="H22" s="13" t="s">
+        <v>202</v>
+      </c>
+      <c r="I22" s="13" t="s">
+        <v>203</v>
+      </c>
+      <c r="J22" s="13" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A23" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="B23" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="C23" s="14">
+        <v>46272</v>
+      </c>
+      <c r="D23" s="13">
+        <v>3182345609</v>
+      </c>
+      <c r="E23" s="13" t="s">
+        <v>74</v>
+      </c>
+      <c r="F23" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="G23" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="H23" s="13" t="s">
+        <v>171</v>
+      </c>
+      <c r="I23" s="13" t="s">
+        <v>161</v>
+      </c>
+      <c r="J23" s="13" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A24" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="B24" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="C24" s="14">
+        <v>46272</v>
+      </c>
+      <c r="D24" s="13">
+        <v>3182345609</v>
+      </c>
+      <c r="E24" s="13" t="s">
+        <v>74</v>
+      </c>
+      <c r="F24" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="G24" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="H24" s="13" t="s">
+        <v>157</v>
+      </c>
+      <c r="I24" s="13" t="s">
+        <v>204</v>
+      </c>
+      <c r="J24" s="13" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A25" s="16" t="s">
+        <v>29</v>
+      </c>
+      <c r="B25" s="16" t="s">
+        <v>30</v>
+      </c>
+      <c r="C25" s="17">
+        <v>46272</v>
+      </c>
+      <c r="D25" s="16">
+        <v>3193456710</v>
+      </c>
+      <c r="E25" s="16" t="s">
+        <v>73</v>
+      </c>
+      <c r="F25" s="18" t="s">
+        <v>52</v>
+      </c>
+      <c r="G25" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="H25" s="16" t="s">
+        <v>170</v>
+      </c>
+      <c r="I25" s="16" t="s">
+        <v>208</v>
+      </c>
+      <c r="J25" s="16" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A26" s="16" t="s">
+        <v>29</v>
+      </c>
+      <c r="B26" s="16" t="s">
+        <v>30</v>
+      </c>
+      <c r="C26" s="17">
+        <v>46272</v>
+      </c>
+      <c r="D26" s="16">
+        <v>3193456710</v>
+      </c>
+      <c r="E26" s="16" t="s">
+        <v>73</v>
+      </c>
+      <c r="F26" s="18" t="s">
+        <v>52</v>
+      </c>
+      <c r="G26" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="H26" s="16" t="s">
+        <v>158</v>
+      </c>
+      <c r="I26" s="16" t="s">
+        <v>159</v>
+      </c>
+      <c r="J26" s="16" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A27" s="16" t="s">
+        <v>29</v>
+      </c>
+      <c r="B27" s="16" t="s">
+        <v>30</v>
+      </c>
+      <c r="C27" s="17">
+        <v>46272</v>
+      </c>
+      <c r="D27" s="16">
+        <v>3193456710</v>
+      </c>
+      <c r="E27" s="16" t="s">
+        <v>73</v>
+      </c>
+      <c r="F27" s="18" t="s">
+        <v>52</v>
+      </c>
+      <c r="G27" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="H27" s="16" t="s">
+        <v>177</v>
+      </c>
+      <c r="I27" s="16" t="s">
+        <v>209</v>
+      </c>
+      <c r="J27" s="16" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A28" s="31" t="s">
+        <v>31</v>
+      </c>
+      <c r="B28" s="31" t="s">
+        <v>147</v>
+      </c>
+      <c r="C28" s="32">
+        <v>46272</v>
+      </c>
+      <c r="D28" s="31">
+        <v>3004567821</v>
+      </c>
+      <c r="E28" s="31" t="s">
+        <v>72</v>
+      </c>
+      <c r="F28" s="33" t="s">
+        <v>54</v>
+      </c>
+      <c r="G28" s="31" t="s">
+        <v>32</v>
+      </c>
+      <c r="H28" s="31" t="s">
+        <v>157</v>
+      </c>
+      <c r="I28" s="31" t="s">
+        <v>190</v>
+      </c>
+      <c r="J28" s="31" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A29" s="31" t="s">
+        <v>31</v>
+      </c>
+      <c r="B29" s="31" t="s">
+        <v>147</v>
+      </c>
+      <c r="C29" s="32">
+        <v>46272</v>
+      </c>
+      <c r="D29" s="31">
+        <v>3004567821</v>
+      </c>
+      <c r="E29" s="31" t="s">
+        <v>72</v>
+      </c>
+      <c r="F29" s="33" t="s">
+        <v>54</v>
+      </c>
+      <c r="G29" s="31" t="s">
+        <v>32</v>
+      </c>
+      <c r="H29" s="31" t="s">
+        <v>171</v>
+      </c>
+      <c r="I29" s="31" t="s">
+        <v>173</v>
+      </c>
+      <c r="J29" s="31" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A30" s="34" t="s">
+        <v>33</v>
+      </c>
+      <c r="B30" s="34" t="s">
+        <v>34</v>
+      </c>
+      <c r="C30" s="35">
+        <v>46272</v>
+      </c>
+      <c r="D30" s="34">
+        <v>3015678932</v>
+      </c>
+      <c r="E30" s="34" t="s">
+        <v>71</v>
+      </c>
+      <c r="F30" s="36" t="s">
+        <v>55</v>
+      </c>
+      <c r="G30" s="34" t="s">
+        <v>28</v>
+      </c>
+      <c r="H30" s="34" t="s">
+        <v>171</v>
+      </c>
+      <c r="I30" s="34" t="s">
+        <v>197</v>
+      </c>
+      <c r="J30" s="34" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A31" s="34" t="s">
+        <v>33</v>
+      </c>
+      <c r="B31" s="34" t="s">
+        <v>34</v>
+      </c>
+      <c r="C31" s="35">
+        <v>46272</v>
+      </c>
+      <c r="D31" s="34">
+        <v>3015678932</v>
+      </c>
+      <c r="E31" s="34" t="s">
+        <v>71</v>
+      </c>
+      <c r="F31" s="36" t="s">
+        <v>55</v>
+      </c>
+      <c r="G31" s="34" t="s">
+        <v>28</v>
+      </c>
+      <c r="H31" s="34" t="s">
+        <v>170</v>
+      </c>
+      <c r="I31" s="34" t="s">
+        <v>6</v>
+      </c>
+      <c r="J31" s="34" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A32" s="34" t="s">
+        <v>33</v>
+      </c>
+      <c r="B32" s="34" t="s">
+        <v>34</v>
+      </c>
+      <c r="C32" s="35">
+        <v>46272</v>
+      </c>
+      <c r="D32" s="34">
+        <v>3015678932</v>
+      </c>
+      <c r="E32" s="34" t="s">
+        <v>71</v>
+      </c>
+      <c r="F32" s="36" t="s">
+        <v>55</v>
+      </c>
+      <c r="G32" s="34" t="s">
+        <v>28</v>
+      </c>
+      <c r="H32" s="34" t="s">
+        <v>165</v>
+      </c>
+      <c r="I32" s="34" t="s">
+        <v>200</v>
+      </c>
+      <c r="J32" s="34" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A33" s="37" t="s">
+        <v>35</v>
+      </c>
+      <c r="B33" s="37" t="s">
+        <v>153</v>
+      </c>
+      <c r="C33" s="38">
+        <v>46272</v>
+      </c>
+      <c r="D33" s="37">
+        <v>3026789043</v>
+      </c>
+      <c r="E33" s="37" t="s">
+        <v>70</v>
+      </c>
+      <c r="F33" s="39" t="s">
+        <v>56</v>
+      </c>
+      <c r="G33" s="37" t="s">
+        <v>63</v>
+      </c>
+      <c r="H33" s="37" t="s">
+        <v>158</v>
+      </c>
+      <c r="I33" s="37" t="s">
+        <v>198</v>
+      </c>
+      <c r="J33" s="37" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A34" s="37" t="s">
+        <v>35</v>
+      </c>
+      <c r="B34" s="37" t="s">
+        <v>153</v>
+      </c>
+      <c r="C34" s="38">
+        <v>46272</v>
+      </c>
+      <c r="D34" s="37">
+        <v>3026789043</v>
+      </c>
+      <c r="E34" s="37" t="s">
+        <v>70</v>
+      </c>
+      <c r="F34" s="39" t="s">
+        <v>56</v>
+      </c>
+      <c r="G34" s="37" t="s">
+        <v>63</v>
+      </c>
+      <c r="H34" s="37" t="s">
+        <v>177</v>
+      </c>
+      <c r="I34" s="37" t="s">
+        <v>217</v>
+      </c>
+      <c r="J34" s="37" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A35" s="37" t="s">
+        <v>35</v>
+      </c>
+      <c r="B35" s="37" t="s">
+        <v>153</v>
+      </c>
+      <c r="C35" s="38">
+        <v>46272</v>
+      </c>
+      <c r="D35" s="37">
+        <v>3026789043</v>
+      </c>
+      <c r="E35" s="37" t="s">
+        <v>70</v>
+      </c>
+      <c r="F35" s="39" t="s">
+        <v>56</v>
+      </c>
+      <c r="G35" s="37" t="s">
+        <v>63</v>
+      </c>
+      <c r="H35" s="37" t="s">
+        <v>164</v>
+      </c>
+      <c r="I35" s="37" t="s">
+        <v>216</v>
+      </c>
+      <c r="J35" s="37" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A36" s="40" t="s">
+        <v>36</v>
+      </c>
+      <c r="B36" s="40" t="s">
+        <v>148</v>
+      </c>
+      <c r="C36" s="41">
+        <v>46272</v>
+      </c>
+      <c r="D36" s="40">
+        <v>3037890154</v>
+      </c>
+      <c r="E36" s="40" t="s">
+        <v>69</v>
+      </c>
+      <c r="F36" s="42" t="s">
+        <v>57</v>
+      </c>
+      <c r="G36" s="40" t="s">
+        <v>37</v>
+      </c>
+      <c r="H36" s="40" t="s">
+        <v>164</v>
+      </c>
+      <c r="I36" s="40" t="s">
+        <v>219</v>
+      </c>
+      <c r="J36" s="40" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A37" s="40" t="s">
+        <v>36</v>
+      </c>
+      <c r="B37" s="40" t="s">
+        <v>148</v>
+      </c>
+      <c r="C37" s="41">
+        <v>46272</v>
+      </c>
+      <c r="D37" s="40">
+        <v>3037890154</v>
+      </c>
+      <c r="E37" s="40" t="s">
+        <v>69</v>
+      </c>
+      <c r="F37" s="42" t="s">
+        <v>57</v>
+      </c>
+      <c r="G37" s="40" t="s">
+        <v>37</v>
+      </c>
+      <c r="H37" s="40" t="s">
+        <v>158</v>
+      </c>
+      <c r="I37" s="40" t="s">
+        <v>159</v>
+      </c>
+      <c r="J37" s="40" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A38" s="19" t="s">
+        <v>38</v>
+      </c>
+      <c r="B38" s="19" t="s">
+        <v>39</v>
+      </c>
+      <c r="C38" s="20">
+        <v>46272</v>
+      </c>
+      <c r="D38" s="19">
+        <v>3048901265</v>
+      </c>
+      <c r="E38" s="19" t="s">
+        <v>68</v>
+      </c>
+      <c r="F38" s="43" t="s">
+        <v>58</v>
+      </c>
+      <c r="G38" s="19" t="s">
+        <v>40</v>
+      </c>
+      <c r="H38" s="19" t="s">
+        <v>165</v>
+      </c>
+      <c r="I38" s="19" t="s">
+        <v>221</v>
+      </c>
+      <c r="J38" s="19" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="19" t="s">
+        <v>38</v>
+      </c>
+      <c r="B39" s="19" t="s">
+        <v>39</v>
+      </c>
+      <c r="C39" s="20">
+        <v>46272</v>
+      </c>
+      <c r="D39" s="19">
+        <v>3048901265</v>
+      </c>
+      <c r="E39" s="19" t="s">
+        <v>68</v>
+      </c>
+      <c r="F39" s="43" t="s">
+        <v>58</v>
+      </c>
+      <c r="G39" s="19" t="s">
+        <v>40</v>
+      </c>
+      <c r="H39" s="19" t="s">
+        <v>170</v>
+      </c>
+      <c r="I39" s="19" t="s">
+        <v>189</v>
+      </c>
+      <c r="J39" s="19" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A40" s="19" t="s">
+        <v>38</v>
+      </c>
+      <c r="B40" s="19" t="s">
+        <v>39</v>
+      </c>
+      <c r="C40" s="20">
+        <v>46272</v>
+      </c>
+      <c r="D40" s="19">
+        <v>3048901265</v>
+      </c>
+      <c r="E40" s="19" t="s">
+        <v>68</v>
+      </c>
+      <c r="F40" s="43" t="s">
+        <v>58</v>
+      </c>
+      <c r="G40" s="19" t="s">
+        <v>40</v>
+      </c>
+      <c r="H40" s="19" t="s">
+        <v>171</v>
+      </c>
+      <c r="I40" s="19" t="s">
+        <v>179</v>
+      </c>
+      <c r="J40" s="19" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A41" s="44" t="s">
+        <v>41</v>
+      </c>
+      <c r="B41" s="44" t="s">
+        <v>149</v>
+      </c>
+      <c r="C41" s="45">
+        <v>46272</v>
+      </c>
+      <c r="D41" s="44">
+        <v>3059012376</v>
+      </c>
+      <c r="E41" s="44" t="s">
+        <v>82</v>
+      </c>
+      <c r="F41" s="46" t="s">
+        <v>59</v>
+      </c>
+      <c r="G41" s="44" t="s">
+        <v>63</v>
+      </c>
+      <c r="H41" s="44" t="s">
+        <v>171</v>
+      </c>
+      <c r="I41" s="44" t="s">
+        <v>223</v>
+      </c>
+      <c r="J41" s="44" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A42" s="44" t="s">
+        <v>41</v>
+      </c>
+      <c r="B42" s="44" t="s">
+        <v>149</v>
+      </c>
+      <c r="C42" s="45">
+        <v>46272</v>
+      </c>
+      <c r="D42" s="44">
+        <v>3059012376</v>
+      </c>
+      <c r="E42" s="44" t="s">
+        <v>82</v>
+      </c>
+      <c r="F42" s="46" t="s">
+        <v>59</v>
+      </c>
+      <c r="G42" s="44" t="s">
+        <v>63</v>
+      </c>
+      <c r="H42" s="44" t="s">
+        <v>157</v>
+      </c>
+      <c r="I42" s="44" t="s">
+        <v>199</v>
+      </c>
+      <c r="J42" s="44" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A43" s="47" t="s">
+        <v>42</v>
+      </c>
+      <c r="B43" s="47" t="s">
+        <v>150</v>
+      </c>
+      <c r="C43" s="48">
+        <v>46272</v>
+      </c>
+      <c r="D43" s="47">
+        <v>3060123487</v>
+      </c>
+      <c r="E43" s="47" t="s">
+        <v>83</v>
+      </c>
+      <c r="F43" s="49" t="s">
+        <v>60</v>
+      </c>
+      <c r="G43" s="47" t="s">
+        <v>28</v>
+      </c>
+      <c r="H43" s="47" t="s">
+        <v>164</v>
+      </c>
+      <c r="I43" s="47" t="s">
+        <v>216</v>
+      </c>
+      <c r="J43" s="47" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A44" s="47" t="s">
+        <v>42</v>
+      </c>
+      <c r="B44" s="47" t="s">
+        <v>150</v>
+      </c>
+      <c r="C44" s="48">
+        <v>46272</v>
+      </c>
+      <c r="D44" s="47">
+        <v>3060123487</v>
+      </c>
+      <c r="E44" s="47" t="s">
+        <v>83</v>
+      </c>
+      <c r="F44" s="49" t="s">
+        <v>60</v>
+      </c>
+      <c r="G44" s="47" t="s">
+        <v>28</v>
+      </c>
+      <c r="H44" s="47" t="s">
+        <v>165</v>
+      </c>
+      <c r="I44" s="47" t="s">
+        <v>200</v>
+      </c>
+      <c r="J44" s="47" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A45" s="47" t="s">
+        <v>42</v>
+      </c>
+      <c r="B45" s="47" t="s">
+        <v>150</v>
+      </c>
+      <c r="C45" s="48">
+        <v>46272</v>
+      </c>
+      <c r="D45" s="47">
+        <v>3060123487</v>
+      </c>
+      <c r="E45" s="47" t="s">
+        <v>83</v>
+      </c>
+      <c r="F45" s="49" t="s">
+        <v>60</v>
+      </c>
+      <c r="G45" s="47" t="s">
+        <v>28</v>
+      </c>
+      <c r="H45" s="47" t="s">
+        <v>158</v>
+      </c>
+      <c r="I45" s="47" t="s">
+        <v>198</v>
+      </c>
+      <c r="J45" s="47" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A46" s="50" t="s">
+        <v>43</v>
+      </c>
+      <c r="B46" s="50" t="s">
+        <v>151</v>
+      </c>
+      <c r="C46" s="51">
+        <v>46272</v>
+      </c>
+      <c r="D46" s="50">
+        <v>3071234598</v>
+      </c>
+      <c r="E46" s="50" t="s">
+        <v>84</v>
+      </c>
+      <c r="F46" s="52" t="s">
+        <v>61</v>
+      </c>
+      <c r="G46" s="50" t="s">
+        <v>44</v>
+      </c>
+      <c r="H46" s="50" t="s">
+        <v>157</v>
+      </c>
+      <c r="I46" s="50" t="s">
+        <v>204</v>
+      </c>
+      <c r="J46" s="50" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A47" s="50" t="s">
+        <v>43</v>
+      </c>
+      <c r="B47" s="50" t="s">
+        <v>151</v>
+      </c>
+      <c r="C47" s="51">
+        <v>46272</v>
+      </c>
+      <c r="D47" s="50">
+        <v>3071234598</v>
+      </c>
+      <c r="E47" s="50" t="s">
+        <v>84</v>
+      </c>
+      <c r="F47" s="52" t="s">
+        <v>61</v>
+      </c>
+      <c r="G47" s="50" t="s">
+        <v>44</v>
+      </c>
+      <c r="H47" s="50" t="s">
+        <v>170</v>
+      </c>
+      <c r="I47" s="50" t="s">
+        <v>189</v>
+      </c>
+      <c r="J47" s="50" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A48" s="16" t="s">
+        <v>45</v>
+      </c>
+      <c r="B48" s="16" t="s">
+        <v>46</v>
+      </c>
+      <c r="C48" s="17">
+        <v>46272</v>
+      </c>
+      <c r="D48" s="16">
+        <v>3082345609</v>
+      </c>
+      <c r="E48" s="16" t="s">
+        <v>85</v>
+      </c>
+      <c r="F48" s="18" t="s">
+        <v>62</v>
+      </c>
+      <c r="G48" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="H48" s="16" t="s">
+        <v>170</v>
+      </c>
+      <c r="I48" s="16" t="s">
+        <v>208</v>
+      </c>
+      <c r="J48" s="16" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A49" s="16" t="s">
+        <v>45</v>
+      </c>
+      <c r="B49" s="16" t="s">
+        <v>46</v>
+      </c>
+      <c r="C49" s="17">
+        <v>46272</v>
+      </c>
+      <c r="D49" s="16">
+        <v>3082345609</v>
+      </c>
+      <c r="E49" s="16" t="s">
+        <v>85</v>
+      </c>
+      <c r="F49" s="18" t="s">
+        <v>62</v>
+      </c>
+      <c r="G49" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="H49" s="16" t="s">
+        <v>171</v>
+      </c>
+      <c r="I49" s="16" t="s">
+        <v>161</v>
+      </c>
+      <c r="J49" s="16" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="50" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A50" s="16" t="s">
+        <v>45</v>
+      </c>
+      <c r="B50" s="16" t="s">
+        <v>46</v>
+      </c>
+      <c r="C50" s="17">
+        <v>46272</v>
+      </c>
+      <c r="D50" s="16">
+        <v>3082345609</v>
+      </c>
+      <c r="E50" s="16" t="s">
+        <v>85</v>
+      </c>
+      <c r="F50" s="18" t="s">
+        <v>62</v>
+      </c>
+      <c r="G50" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="H50" s="16" t="s">
+        <v>177</v>
+      </c>
+      <c r="I50" s="16" t="s">
+        <v>209</v>
+      </c>
+      <c r="J50" s="16" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="54" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A54" s="1"/>
+      <c r="B54" s="1"/>
+      <c r="C54" s="1"/>
+      <c r="D54" s="1"/>
+      <c r="E54" s="1"/>
+      <c r="F54" s="1"/>
+      <c r="G54" s="1"/>
+    </row>
+    <row r="55" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A55" s="2"/>
+      <c r="B55" s="2"/>
+      <c r="C55" s="3"/>
+      <c r="D55" s="2"/>
+      <c r="E55" s="2"/>
+      <c r="F55" s="4"/>
+      <c r="G55" s="2"/>
+    </row>
+    <row r="56" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A56" s="2"/>
+      <c r="B56" s="2"/>
+      <c r="C56" s="3"/>
+      <c r="D56" s="2"/>
+      <c r="E56" s="2"/>
+      <c r="F56" s="4"/>
+      <c r="G56" s="2"/>
+    </row>
+    <row r="57" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A57" s="2"/>
+      <c r="B57" s="2"/>
+      <c r="C57" s="3"/>
+      <c r="D57" s="2"/>
+      <c r="E57" s="2"/>
+      <c r="F57" s="4"/>
+      <c r="G57" s="2"/>
+    </row>
+    <row r="58" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A58" s="2"/>
+      <c r="B58" s="2"/>
+      <c r="C58" s="3"/>
+      <c r="D58" s="2"/>
+      <c r="E58" s="2"/>
+      <c r="F58" s="4"/>
+      <c r="G58" s="2"/>
+    </row>
+    <row r="59" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A59" s="2"/>
+      <c r="B59" s="2"/>
+      <c r="C59" s="3"/>
+      <c r="D59" s="2"/>
+      <c r="E59" s="2"/>
+      <c r="F59" s="4"/>
+      <c r="G59" s="2"/>
+    </row>
+    <row r="60" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A60" s="2"/>
+      <c r="B60" s="2"/>
+      <c r="C60" s="3"/>
+      <c r="D60" s="2"/>
+      <c r="E60" s="2"/>
+      <c r="F60" s="4"/>
+      <c r="G60" s="2"/>
+    </row>
+    <row r="61" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A61" s="2"/>
+      <c r="B61" s="2"/>
+      <c r="C61" s="3"/>
+      <c r="D61" s="2"/>
+      <c r="E61" s="2"/>
+      <c r="F61" s="4"/>
+      <c r="G61" s="2"/>
+    </row>
+    <row r="62" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A62" s="2"/>
+      <c r="B62" s="2"/>
+      <c r="C62" s="3"/>
+      <c r="D62" s="2"/>
+      <c r="E62" s="2"/>
+      <c r="F62" s="4"/>
+      <c r="G62" s="2"/>
+    </row>
+    <row r="63" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A63" s="2"/>
+      <c r="B63" s="2"/>
+      <c r="C63" s="3"/>
+      <c r="D63" s="2"/>
+      <c r="E63" s="2"/>
+      <c r="F63" s="4"/>
+      <c r="G63" s="2"/>
+    </row>
+    <row r="64" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A64" s="2"/>
+      <c r="B64" s="2"/>
+      <c r="C64" s="3"/>
+      <c r="D64" s="2"/>
+      <c r="E64" s="2"/>
+      <c r="F64" s="4"/>
+      <c r="G64" s="2"/>
+    </row>
+    <row r="65" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A65" s="2"/>
+      <c r="B65" s="2"/>
+      <c r="C65" s="3"/>
+      <c r="D65" s="2"/>
+      <c r="E65" s="2"/>
+      <c r="F65" s="4"/>
+      <c r="G65" s="2"/>
+    </row>
+    <row r="66" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A66" s="2"/>
+      <c r="B66" s="2"/>
+      <c r="C66" s="3"/>
+      <c r="D66" s="2"/>
+      <c r="E66" s="2"/>
+      <c r="F66" s="4"/>
+      <c r="G66" s="2"/>
+    </row>
+    <row r="67" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A67" s="2"/>
+      <c r="B67" s="2"/>
+      <c r="C67" s="3"/>
+      <c r="D67" s="2"/>
+      <c r="E67" s="2"/>
+      <c r="F67" s="4"/>
+      <c r="G67" s="2"/>
+    </row>
+    <row r="68" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A68" s="2"/>
+      <c r="B68" s="2"/>
+      <c r="C68" s="3"/>
+      <c r="D68" s="2"/>
+      <c r="E68" s="2"/>
+      <c r="F68" s="4"/>
+      <c r="G68" s="2"/>
+    </row>
+    <row r="69" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A69" s="2"/>
+      <c r="B69" s="2"/>
+      <c r="C69" s="3"/>
+      <c r="D69" s="2"/>
+      <c r="E69" s="2"/>
+      <c r="F69" s="4"/>
+      <c r="G69" s="2"/>
+    </row>
+    <row r="70" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A70" s="2"/>
+      <c r="B70" s="2"/>
+      <c r="C70" s="3"/>
+      <c r="D70" s="2"/>
+      <c r="E70" s="2"/>
+      <c r="F70" s="4"/>
+      <c r="G70" s="2"/>
+    </row>
+    <row r="71" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A71" s="2"/>
+      <c r="B71" s="2"/>
+      <c r="C71" s="3"/>
+      <c r="D71" s="2"/>
+      <c r="E71" s="2"/>
+      <c r="F71" s="4"/>
+      <c r="G71" s="2"/>
+    </row>
+    <row r="72" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A72" s="2"/>
+      <c r="B72" s="2"/>
+      <c r="C72" s="3"/>
+      <c r="D72" s="2"/>
+      <c r="E72" s="2"/>
+      <c r="F72" s="4"/>
+      <c r="G72" s="2"/>
+    </row>
+    <row r="73" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A73" s="2"/>
+      <c r="B73" s="2"/>
+      <c r="C73" s="3"/>
+      <c r="D73" s="2"/>
+      <c r="E73" s="2"/>
+      <c r="F73" s="4"/>
+      <c r="G73" s="2"/>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="F6" r:id="rId1" xr:uid="{34EAAE86-D9B3-4B90-A393-528CB61C96D4}"/>
+    <hyperlink ref="F9" r:id="rId2" xr:uid="{6AD7BB9B-F011-4C1A-AAE3-597C886FCABD}"/>
+    <hyperlink ref="F20" r:id="rId3" xr:uid="{3261E6EC-C209-4B00-8F90-F2C441063352}"/>
+    <hyperlink ref="F22" r:id="rId4" xr:uid="{402180B7-A8D1-4330-9307-3BF0801ECBAE}"/>
+    <hyperlink ref="F25" r:id="rId5" xr:uid="{9D05D043-F913-40FC-AAA1-EF675A15F55C}"/>
+    <hyperlink ref="F17" r:id="rId6" xr:uid="{CD80FA62-7539-4313-9FDF-BC18B80643CF}"/>
+    <hyperlink ref="F28" r:id="rId7" xr:uid="{31C5C59B-A6A9-4C1F-9AC5-0669CB7F5002}"/>
+    <hyperlink ref="F30" r:id="rId8" xr:uid="{F562B2FC-1B84-47B0-9D14-CBF7BDD08459}"/>
+    <hyperlink ref="F33" r:id="rId9" xr:uid="{697F835E-65A9-46F5-83E3-37D957E58C4D}"/>
+    <hyperlink ref="F36" r:id="rId10" xr:uid="{13D2B9A4-ADD7-41D5-AE05-7EB82C06B719}"/>
+    <hyperlink ref="F38" r:id="rId11" xr:uid="{00C40D2E-1208-4F03-9A7D-59E38CBBCA82}"/>
+    <hyperlink ref="F41" r:id="rId12" xr:uid="{3F2B0613-5A00-4925-8504-DC8431BCEFBA}"/>
+    <hyperlink ref="F43" r:id="rId13" xr:uid="{7DD8D305-706D-4224-9FA4-094DF0D4F411}"/>
+    <hyperlink ref="F46" r:id="rId14" xr:uid="{6E2CEFFA-34E7-40C4-829F-7E233E480D20}"/>
+    <hyperlink ref="F50" r:id="rId15" xr:uid="{D32060C5-0DF1-4DBD-8419-6F6727B19C4E}"/>
+    <hyperlink ref="F15" r:id="rId16" xr:uid="{1E2D7C66-C379-4C95-8789-94F4AF6D964B}"/>
+    <hyperlink ref="F12" r:id="rId17" xr:uid="{77FA4C6D-79DD-4684-8C69-22810FCDDB0B}"/>
+    <hyperlink ref="F11" r:id="rId18" xr:uid="{DFEE46E7-EB6E-46CF-8EA1-EEB2D0ECF306}"/>
+    <hyperlink ref="F5" r:id="rId19" xr:uid="{7E42D66A-1CE7-439E-8D19-E62A4D0A9B4F}"/>
+    <hyperlink ref="F7" r:id="rId20" xr:uid="{7612018C-07BF-4542-AAA3-1D853F307061}"/>
+    <hyperlink ref="F8" r:id="rId21" xr:uid="{C17047DB-5F19-4C4E-BDF0-AE1EF382C188}"/>
+    <hyperlink ref="F10" r:id="rId22" xr:uid="{FED372ED-AAB4-495C-8E43-46C1ACE62826}"/>
+    <hyperlink ref="F13" r:id="rId23" xr:uid="{D4B3E7B5-6279-49EB-BA4C-CA1C52D901E3}"/>
+    <hyperlink ref="F14" r:id="rId24" xr:uid="{414FA45B-B6C2-4547-A4F3-3D5B3013E380}"/>
+    <hyperlink ref="F16" r:id="rId25" xr:uid="{78ABE284-0195-4736-9BE4-2705CB151723}"/>
+    <hyperlink ref="F18" r:id="rId26" xr:uid="{7ADFE529-48A5-4A62-BB7D-33AE59E23E77}"/>
+    <hyperlink ref="F19" r:id="rId27" xr:uid="{D4DE7232-F9A2-4A49-830A-3D96780BB3FB}"/>
+    <hyperlink ref="F21" r:id="rId28" xr:uid="{6D80602D-C0A7-43F0-9A1A-50498D048F38}"/>
+    <hyperlink ref="F23" r:id="rId29" xr:uid="{4BAEC725-E405-4E24-BE08-B2AD602C4F54}"/>
+    <hyperlink ref="F24" r:id="rId30" xr:uid="{AEAE7298-8C09-4FFB-ABB2-1DBB7668F5AD}"/>
+    <hyperlink ref="F26" r:id="rId31" xr:uid="{2EEC9954-1E6B-4253-B09F-1CCB4F911D37}"/>
+    <hyperlink ref="F27" r:id="rId32" xr:uid="{9B09ACFF-1323-4A82-8538-54D9555929C3}"/>
+    <hyperlink ref="F29" r:id="rId33" xr:uid="{591F2E5E-D3E9-4C69-9A75-19A38FA3705D}"/>
+    <hyperlink ref="F31" r:id="rId34" xr:uid="{B36B919A-8E13-4034-8B88-6566C5B75D99}"/>
+    <hyperlink ref="F32" r:id="rId35" xr:uid="{71CD9DE1-C4F8-47DF-B754-29FE8EAD24D1}"/>
+    <hyperlink ref="F34" r:id="rId36" xr:uid="{90415089-C247-4AEA-B222-9B1EE04CA4FE}"/>
+    <hyperlink ref="F35" r:id="rId37" xr:uid="{9EE532AC-7D28-4247-AE6D-9D6A01FBEFE3}"/>
+    <hyperlink ref="F37" r:id="rId38" xr:uid="{651BCE86-BB6C-4365-BB9D-77193328CE96}"/>
+    <hyperlink ref="F39" r:id="rId39" xr:uid="{224ACA18-A924-4782-8C00-71D2B6ACF2A1}"/>
+    <hyperlink ref="F40" r:id="rId40" xr:uid="{65FD7E56-DE89-43C2-8048-5F02F24D074B}"/>
+    <hyperlink ref="F42" r:id="rId41" xr:uid="{AAF35B5A-C0C1-4BB0-8D26-DCFD3859C18D}"/>
+    <hyperlink ref="F44" r:id="rId42" xr:uid="{4552A220-991A-4125-8203-36E460E5D928}"/>
+    <hyperlink ref="F45" r:id="rId43" xr:uid="{99D7D0E9-EF25-456B-B70B-67A1C09F6C4A}"/>
+    <hyperlink ref="F48" r:id="rId44" xr:uid="{0919847E-25F4-4C6A-ABA9-B1FF768EDA04}"/>
+    <hyperlink ref="F49" r:id="rId45" xr:uid="{18CF1C5A-CE5F-4571-AE6B-9CAE09FB8D2A}"/>
+    <hyperlink ref="F47" r:id="rId46" xr:uid="{A89737A0-7074-4803-B58E-2EFE95F4F646}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId47"/>
 </worksheet>
 </file>
--- a/ComponentesMetodologicos/Normalizacion.xlsx
+++ b/ComponentesMetodologicos/Normalizacion.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SENA\Desktop\CEREBRUM\PROYECTO_CEREBRUM\ComponentesMetodologicos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89B42DB8-6633-4535-919B-00370A3EEF4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C00C0338-CCAD-4559-9F9A-D7C394E6168D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13140" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
